--- a/FILE_1_SPREADSHEET_AKIP_2025_LOKASI_FILE_LAPTOP.xlsx
+++ b/FILE_1_SPREADSHEET_AKIP_2025_LOKASI_FILE_LAPTOP.xlsx
@@ -5770,7 +5770,7 @@
       </c>
       <c r="H93" s="52" t="inlineStr">
         <is>
-          <t>http://ppid.pktj.ac.id/admin/prosedur/sop-permintaan</t>
+          <t>http://ppid.pktj.ac.id/admin/layanan/aksesibilitas</t>
         </is>
       </c>
       <c r="I93" s="52" t="n"/>
@@ -5818,22 +5818,22 @@
       </c>
       <c r="E94" s="16" t="inlineStr">
         <is>
-          <t>Inovasi Formulir Layanan Braille, Audio Text-to-Speech, &amp; Video Panduan Bahasa Isyarat</t>
+          <t>Dokumen Formulir Permohonan &amp; Keberatan Huruf Braille serta Laporan Inovasi Layanan Ramah Disabilitas PPID PKTJ Tegal</t>
         </is>
       </c>
       <c r="F94" s="16" t="inlineStr">
         <is>
-          <t>Inovasi inklusivitas pelayanan informasi publik bagi penyandang disabilitas tunanetra, tunarungu, dan tunawicara.</t>
+          <t>Inovasi pemenuhan sarana aksesibilitas terpadu bagi penyandang disabilitas: Formulir Permohonan Braille, Pernyataan Keberatan Braille, Audio Text-to-Speech otomatis, serta Video Panduan Bahasa Isyarat (Bisindo).</t>
         </is>
       </c>
       <c r="G94" s="16" t="inlineStr">
         <is>
-          <t>FORMULIR PERMOHONAN BRAILLE.pdf &amp; Inovasi PPID.docx (Path: AKIP PKTJ 2025\Indikator I\FORMULIR PERMOHONAN INFORMASI PUBLIK BRAILE.pdf &amp; Inovasi PPID.docx)</t>
+          <t>FORMULIR PERMOHONAN BRAILE.pdf, PERNYATAAN KEBERATAN BRAILE.pdf, &amp; Inovasi PPID.docx (Path: AKIP PKTJ 2025\Indikator I\FORMULIR PERMOHONAN BRAILE.pdf, PERNYATAAN KEBERATAN BRAILE.pdf, &amp; Inovasi PPID.docx)</t>
         </is>
       </c>
       <c r="H94" s="52" t="inlineStr">
         <is>
-          <t>http://ppid.pktj.ac.id/admin/prosedur/sop-permintaan</t>
+          <t>http://ppid.pktj.ac.id/admin/layanan/aksesibilitas</t>
         </is>
       </c>
       <c r="I94" s="52" t="n"/>

--- a/FILE_1_SPREADSHEET_AKIP_2025_LOKASI_FILE_LAPTOP.xlsx
+++ b/FILE_1_SPREADSHEET_AKIP_2025_LOKASI_FILE_LAPTOP.xlsx
@@ -618,7 +618,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AB1044"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="3.13" customWidth="1" style="53" min="1" max="1"/>
     <col width="8" customWidth="1" style="53" min="2" max="2"/>
@@ -5818,17 +5818,17 @@
       </c>
       <c r="E94" s="16" t="inlineStr">
         <is>
-          <t>Dokumen Formulir Permohonan &amp; Keberatan Huruf Braille serta Laporan Inovasi Layanan Ramah Disabilitas PPID PKTJ Tegal</t>
+          <t>Dokumen Formulir Permohonan &amp; Keberatan Huruf Braille (Standar &amp; Full) serta Laporan Inovasi Layanan Ramah Disabilitas PPID PKTJ Tegal</t>
         </is>
       </c>
       <c r="F94" s="16" t="inlineStr">
         <is>
-          <t>Inovasi pemenuhan sarana aksesibilitas terpadu bagi penyandang disabilitas: Formulir Permohonan Braille, Pernyataan Keberatan Braille, Audio Text-to-Speech otomatis, serta Video Panduan Bahasa Isyarat (Bisindo).</t>
+          <t>Inovasi pemenuhan sarana aksesibilitas terpadu bagi penyandang disabilitas: Formulir Permohonan Braille (Standar &amp; Full Format), Pernyataan Keberatan Braille (Standar &amp; Full Format), Audio Text-to-Speech otomatis, serta Video Panduan Bahasa Isyarat (Bisindo). Diunggah/diinput linknya melalui Menu Admin Layanan Inklusif (Braille).</t>
         </is>
       </c>
       <c r="G94" s="16" t="inlineStr">
         <is>
-          <t>FORMULIR PERMOHONAN BRAILE.pdf, PERNYATAAN KEBERATAN BRAILE.pdf, &amp; Inovasi PPID.docx (Path: AKIP PKTJ 2025\Indikator I\FORMULIR PERMOHONAN BRAILE.pdf, PERNYATAAN KEBERATAN BRAILE.pdf, &amp; Inovasi PPID.docx)</t>
+          <t>FORMULIR PERMOHONAN INFORMASI PUBLIK BRAILE.pdf, FORMULIR PERMOHONAN INFORMASI PUBLIK FULL BRAILE.pdf, PERNYATAAN KEBERATAN ATAS PERMOHONAN INFORMASI BRAILE.pdf, PERNYATAAN KEBERATAN ATAS PERMOHONAN INFORMASI FULL BRAILE.pdf, &amp; Inovasi PPID.docx (Path: AKIP PKTJ 2025\Indikator I)</t>
         </is>
       </c>
       <c r="H94" s="52" t="inlineStr">

--- a/FILE_1_SPREADSHEET_AKIP_2025_LOKASI_FILE_LAPTOP.xlsx
+++ b/FILE_1_SPREADSHEET_AKIP_2025_LOKASI_FILE_LAPTOP.xlsx
@@ -17,7 +17,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d.m"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="33">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -150,8 +150,50 @@
       <color rgb="FFFF0000"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00137333"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00137333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C5221F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C5221F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -170,8 +212,38 @@
         <bgColor rgb="FFDCDCEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE8E6"/>
+        <bgColor rgb="00FCE8E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00002B5C"/>
+        <bgColor rgb="00002B5C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border/>
     <border>
       <left style="thin">
@@ -187,11 +259,25 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -342,6 +428,128 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -620,13 +828,16 @@
   <dimension ref="A1:AB1044"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
-    <col width="3.13" customWidth="1" style="53" min="1" max="1"/>
-    <col width="8" customWidth="1" style="53" min="2" max="2"/>
-    <col width="81.5" customWidth="1" style="53" min="3" max="3"/>
-    <col width="47.5" customWidth="1" style="53" min="5" max="5"/>
-    <col width="39.88" customWidth="1" style="53" min="6" max="6"/>
-    <col width="48" customWidth="1" style="53" min="7" max="7"/>
-    <col width="51.5" customWidth="1" style="53" min="10" max="10"/>
+    <col width="6" customWidth="1" style="53" min="1" max="1"/>
+    <col width="40" customWidth="1" style="53" min="2" max="2"/>
+    <col width="18" customWidth="1" style="53" min="3" max="3"/>
+    <col width="14" customWidth="1" style="53" min="4" max="4"/>
+    <col width="38" customWidth="1" style="53" min="5" max="5"/>
+    <col width="45" customWidth="1" style="53" min="6" max="6"/>
+    <col width="42" customWidth="1" style="53" min="7" max="7"/>
+    <col width="38" customWidth="1" style="53" min="8" max="8"/>
+    <col width="25" customWidth="1" style="53" min="9" max="9"/>
+    <col width="22" customWidth="1" style="53" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -636,8 +847,15 @@
         </is>
       </c>
       <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
+      <c r="H1" s="54" t="inlineStr">
+        <is>
+          <t>DOKUMEN TERUPLOAD:</t>
+        </is>
+      </c>
+      <c r="I1" s="55">
+        <f>COUNTIF(I5:I105, "*SUDAH*")</f>
+        <v/>
+      </c>
       <c r="J1" s="3" t="n"/>
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
@@ -665,8 +883,15 @@
         </is>
       </c>
       <c r="G2" s="8" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="n"/>
+      <c r="H2" s="56" t="inlineStr">
+        <is>
+          <t>BELUM TERUPLOAD:</t>
+        </is>
+      </c>
+      <c r="I2" s="57">
+        <f>COUNTIF(I5:I105, "*BELUM*")</f>
+        <v/>
+      </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Catatan:</t>
@@ -732,28 +957,36 @@
           <t>Keterangan</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="58" t="inlineStr">
         <is>
           <t>Judul Dokumen Resmi yang Dibuat di Website</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="58" t="inlineStr">
         <is>
           <t>Deskripsi Dokumen di Website</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="58" t="inlineStr">
         <is>
           <t>Nama File &amp; Path di Folder 'AKIP PKTJ 2025'</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="59" t="inlineStr">
         <is>
           <t>Link Langsung Edit di Admin Panel PKTJ</t>
         </is>
       </c>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="n"/>
+      <c r="I4" s="59" t="inlineStr">
+        <is>
+          <t>STATUS UPLOAD (PILIH DROPDOWN / CENTANG)</t>
+        </is>
+      </c>
+      <c r="J4" s="59" t="inlineStr">
+        <is>
+          <t>CATATAN / TANGGAL UPLOAD</t>
+        </is>
+      </c>
       <c r="K4" s="7" t="n"/>
       <c r="L4" s="7" t="n"/>
       <c r="M4" s="7" t="n"/>
@@ -774,32 +1007,36 @@
       <c r="AB4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="52" t="n"/>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="A5" s="60" t="n"/>
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>PPID</t>
         </is>
       </c>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="D5" s="63" t="n"/>
+      <c r="E5" s="63" t="inlineStr">
         <is>
           <t>SEKSI A: PPID (16,5 Poin)</t>
         </is>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16" t="n"/>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="F5" s="63" t="n"/>
+      <c r="G5" s="63" t="n"/>
+      <c r="H5" s="60" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/profil/edit/profil_singkat</t>
         </is>
       </c>
-      <c r="I5" s="52" t="n"/>
-      <c r="J5" s="52" t="inlineStr">
+      <c r="I5" s="60" t="inlineStr">
+        <is>
+          <t>SEKSI A</t>
+        </is>
+      </c>
+      <c r="J5" s="60" t="inlineStr">
         <is>
           <t>Profil</t>
         </is>
@@ -832,42 +1069,46 @@
       <c r="AB5" s="52" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="52" t="n"/>
-      <c r="B6" s="11" t="n">
+      <c r="A6" s="64" t="n"/>
+      <c r="B6" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara telah menunjuk PPID yang mempunyai tugas dan fungsi mengelola informasi publik?</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="67" t="inlineStr">
         <is>
           <t>Surat Keputusan Direktur PKTJ tentang Penetapan Pengelola PPID Pelaksana PKTJ Tegal</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="64" t="inlineStr">
         <is>
           <t>Dokumen penetapan resmi pejabat pengelola informasi dan dokumentasi pelaksana di lingkungan Politeknik Keselamatan Transportasi Jalan Tegal.</t>
         </is>
       </c>
-      <c r="G6" s="39" t="inlineStr">
+      <c r="G6" s="68" t="inlineStr">
         <is>
           <t>A1.pdf (Path: AKIP PKTJ 2025\Indikator A\A1.pdf)</t>
         </is>
       </c>
-      <c r="H6" s="52" t="inlineStr">
+      <c r="H6" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/regulasi</t>
         </is>
       </c>
-      <c r="I6" s="52" t="n"/>
-      <c r="J6" s="52" t="n"/>
+      <c r="I6" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J6" s="70" t="inlineStr"/>
       <c r="K6" s="52" t="n"/>
       <c r="L6" s="52" t="n"/>
       <c r="M6" s="52" t="n"/>
@@ -888,42 +1129,46 @@
       <c r="AB6" s="52" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="52" t="n"/>
-      <c r="B7" s="11" t="n">
+      <c r="A7" s="64" t="n"/>
+      <c r="B7" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengetahui/memiliki/menguasai Peraturan Menteri Perhubungan Nomor 46 tahun 2018 tentang Pedoman Pengelolaan Informasi dan Dokumentasi di Lingkungan Kementerian Perhubungan?</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="67" t="inlineStr">
         <is>
           <t>Peraturan Menteri Perhubungan Nomor PM 46 Tahun 2018 tentang Pedoman Pengelolaan Informasi dan Dokumentasi</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="64" t="inlineStr">
         <is>
           <t>Regulasi induk kementerian mengenai tata kelola dan pedoman standar layanan PPID di seluruh lingkungan Kementerian Perhubungan.</t>
         </is>
       </c>
-      <c r="G7" s="39" t="inlineStr">
+      <c r="G7" s="68" t="inlineStr">
         <is>
           <t>A2.pdf (Path: AKIP PKTJ 2025\Indikator A\A2.pdf)</t>
         </is>
       </c>
-      <c r="H7" s="52" t="inlineStr">
+      <c r="H7" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/regulasi</t>
         </is>
       </c>
-      <c r="I7" s="52" t="n"/>
-      <c r="J7" s="52" t="n"/>
+      <c r="I7" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J7" s="70" t="inlineStr"/>
       <c r="K7" s="52" t="n"/>
       <c r="L7" s="52" t="n"/>
       <c r="M7" s="52" t="n"/>
@@ -944,42 +1189,46 @@
       <c r="AB7" s="52" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="52" t="n"/>
-      <c r="B8" s="11" t="n">
+      <c r="A8" s="64" t="n"/>
+      <c r="B8" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengetahui/memiliki/menguasai Keputusan Menteri Perhubungan Nomor 117 tahun 2022 tentang SOP Pejabat Pengelola Informasi dan Dokumentasi di Lingkungan Kementerian Perhubungan?</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="67" t="inlineStr">
         <is>
           <t>Keputusan Menteri Perhubungan Nomor KM 117 Tahun 2022 tentang SOP PPID Kemenhub</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="64" t="inlineStr">
         <is>
           <t>Standar Operasional Prosedur resmi PPID di lingkungan Kementerian Perhubungan.</t>
         </is>
       </c>
-      <c r="G8" s="39" t="inlineStr">
+      <c r="G8" s="68" t="inlineStr">
         <is>
           <t>A3.pdf (Path: AKIP PKTJ 2025\Indikator A\A3.pdf)</t>
         </is>
       </c>
-      <c r="H8" s="52" t="inlineStr">
+      <c r="H8" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/regulasi</t>
         </is>
       </c>
-      <c r="I8" s="52" t="n"/>
-      <c r="J8" s="52" t="n"/>
+      <c r="I8" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J8" s="70" t="inlineStr"/>
       <c r="K8" s="52" t="n"/>
       <c r="L8" s="52" t="n"/>
       <c r="M8" s="52" t="n"/>
@@ -1000,46 +1249,46 @@
       <c r="AB8" s="52" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="52" t="n"/>
-      <c r="B9" s="11" t="n">
+      <c r="A9" s="64" t="n"/>
+      <c r="B9" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara memiliki informasi mengenai profil singkat tentang organisasi PPID di unit kerja Saudara?</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="71" t="inlineStr">
         <is>
           <t>Profil Singkat Pejabat Pengelola Informasi dan Dokumentasi (PPID) PKTJ Tegal</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" s="72" t="inlineStr">
         <is>
           <t>Narasi sejarah, latar belakang pembentukan, komitmen keterbukaan informasi publik, alamat kantor, peta domisili, dan peran PPID dalam mendukung tugas fungsi PKTJ.</t>
         </is>
       </c>
-      <c r="G9" s="39" t="inlineStr">
+      <c r="G9" s="68" t="inlineStr">
         <is>
           <t>Profil_PPID_PKTJ.pdf (Path: Tayang di Halaman Publik: /profil-ppid.html)</t>
         </is>
       </c>
-      <c r="H9" s="52" t="inlineStr">
+      <c r="H9" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/profil/edit/profil_singkat</t>
         </is>
       </c>
-      <c r="I9" s="52" t="n"/>
-      <c r="J9" s="52" t="inlineStr">
-        <is>
-          <t>Profil diperbaharui dikaitkan dengan tugas fungsi PKTJ, alamat, Map, Struktur organisasi PPID</t>
-        </is>
-      </c>
+      <c r="I9" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J9" s="70" t="inlineStr"/>
       <c r="K9" s="52" t="n"/>
       <c r="L9" s="52" t="n"/>
       <c r="M9" s="52" t="n"/>
@@ -1060,42 +1309,46 @@
       <c r="AB9" s="52" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="52" t="n"/>
-      <c r="B10" s="11" t="n">
+      <c r="A10" s="64" t="n"/>
+      <c r="B10" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara memiliki informasi mengenai Tugas Fungsi PPID?</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="73" t="inlineStr">
         <is>
           <t>Tugas dan Tanggung Jawab PPID Pelaksana PKTJ Tegal</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="64" t="inlineStr">
         <is>
           <t>Rincian tugas pokok, wewenang, dan tanggung jawab PPID Pelaksana UPT PKTJ yang selaras dengan PPID Utama Kemenhub.</t>
         </is>
       </c>
-      <c r="G10" s="39" t="inlineStr">
+      <c r="G10" s="68" t="inlineStr">
         <is>
           <t>Tugas_Fungsi_PPID.pdf (Path: Tayang di Halaman Publik: /profil-tugas-tanggung-jawab.html)</t>
         </is>
       </c>
-      <c r="H10" s="52" t="inlineStr">
+      <c r="H10" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/profil/edit/tugas_fungsi</t>
         </is>
       </c>
-      <c r="I10" s="52" t="n"/>
-      <c r="J10" s="52" t="n"/>
+      <c r="I10" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J10" s="70" t="inlineStr"/>
       <c r="K10" s="52" t="n"/>
       <c r="L10" s="52" t="n"/>
       <c r="M10" s="52" t="n"/>
@@ -1116,46 +1369,46 @@
       <c r="AB10" s="52" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="52" t="n"/>
-      <c r="B11" s="11" t="n">
+      <c r="A11" s="64" t="n"/>
+      <c r="B11" s="65" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara memiliki informasi mengenai Struktur Organisasi PPID?</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="73" t="inlineStr">
         <is>
           <t>Bagan Struktur Organisasi PPID Pelaksana PKTJ Tegal (Sesuai PM 46 Tahun 2018)</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr">
+      <c r="F11" s="72" t="inlineStr">
         <is>
           <t>Bagan kepengurusan PPID UPT: Atasan PPID (Direktur PKTJ), PPID Pelaksana, Pengelola Dokumentasi, dan Petugas Informasi.</t>
         </is>
       </c>
-      <c r="G11" s="39" t="inlineStr">
+      <c r="G11" s="68" t="inlineStr">
         <is>
           <t>A6.jpeg (Path: AKIP PKTJ 2025\Indikator A\A6.jpeg)</t>
         </is>
       </c>
-      <c r="H11" s="52" t="inlineStr">
+      <c r="H11" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/profil/edit/struktur_organisasi</t>
         </is>
       </c>
-      <c r="I11" s="52" t="n"/>
-      <c r="J11" s="52" t="inlineStr">
-        <is>
-          <t>Struktur PPID diperbaharui dan diupload di web</t>
-        </is>
-      </c>
+      <c r="I11" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J11" s="70" t="inlineStr"/>
       <c r="K11" s="52" t="n"/>
       <c r="L11" s="52" t="n"/>
       <c r="M11" s="52" t="n"/>
@@ -1176,42 +1429,46 @@
       <c r="AB11" s="52" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="52" t="n"/>
-      <c r="B12" s="11" t="n">
+      <c r="A12" s="64" t="n"/>
+      <c r="B12" s="65" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara memiliki informasi mengenai Visi Misi PPID?</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="73" t="inlineStr">
         <is>
           <t>Visi dan Misi PPID Pelaksana PKTJ Tegal</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="64" t="inlineStr">
         <is>
           <t>Visi dan Misi pelayanan keterbukaan informasi publik yang transparan, akuntabel, dan berorientasi pelayanan prima.</t>
         </is>
       </c>
-      <c r="G12" s="39" t="inlineStr">
+      <c r="G12" s="68" t="inlineStr">
         <is>
           <t>Visi_Misi_PPID.pdf (Path: Tayang di Halaman Publik: /profil-visi-misi.html)</t>
         </is>
       </c>
-      <c r="H12" s="52" t="inlineStr">
+      <c r="H12" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/profil/edit/visi_misi</t>
         </is>
       </c>
-      <c r="I12" s="52" t="n"/>
-      <c r="J12" s="52" t="n"/>
+      <c r="I12" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J12" s="70" t="inlineStr"/>
       <c r="K12" s="52" t="n"/>
       <c r="L12" s="52" t="n"/>
       <c r="M12" s="52" t="n"/>
@@ -1232,42 +1489,46 @@
       <c r="AB12" s="52" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="52" t="n"/>
-      <c r="B13" s="11" t="n">
+      <c r="A13" s="64" t="n"/>
+      <c r="B13" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyelenggarakan forum, FGD, rapat terkait pengelolaan pelayanan informasi?</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="74" t="inlineStr">
         <is>
           <t>Dokumentasi Foto dan Notulensi Rapat Koordinasi Internal Layanan PPID PKTJ</t>
         </is>
       </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="F13" s="72" t="inlineStr">
         <is>
           <t>Bukti penyelenggaraan rapat koordinasi, forum pembahasan layanan informasi, dan konsolidasi internal PPID PKTJ.</t>
         </is>
       </c>
-      <c r="G13" s="39" t="inlineStr">
+      <c r="G13" s="68" t="inlineStr">
         <is>
           <t>A8.JPG (Path: AKIP PKTJ 2025\Indikator A\A8.JPG)</t>
         </is>
       </c>
-      <c r="H13" s="52" t="inlineStr">
+      <c r="H13" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala/create</t>
         </is>
       </c>
-      <c r="I13" s="52" t="n"/>
-      <c r="J13" s="52" t="n"/>
+      <c r="I13" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J13" s="70" t="inlineStr"/>
       <c r="K13" s="52" t="n"/>
       <c r="L13" s="52" t="n"/>
       <c r="M13" s="52" t="n"/>
@@ -1288,42 +1549,46 @@
       <c r="AB13" s="52" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="52" t="n"/>
-      <c r="B14" s="11" t="n">
+      <c r="A14" s="64" t="n"/>
+      <c r="B14" s="65" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="75" t="inlineStr">
         <is>
           <t>Apakah unit kerja saudara mengikuti kegiatan yang berhubungan dengan pelayanan informasi yang diselenggarakan oleh PPID Utama/PPID Pelaksana?</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="74" t="inlineStr">
         <is>
           <t>Dokumentasi Keikutsertaan Bimbingan Teknis &amp; Evaluasi Monev KIP Kementerian Perhubungan</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="64" t="inlineStr">
         <is>
           <t>Bukti partisipasi aktif pengelola PPID PKTJ dalam bimbingan teknis dan evaluasi keterbukaan informasi Kemenhub.</t>
         </is>
       </c>
-      <c r="G14" s="39" t="inlineStr">
+      <c r="G14" s="68" t="inlineStr">
         <is>
           <t>A9 2024.jpg &amp; A9 2025.jpg (Path: AKIP PKTJ 2025\Indikator A\A9\A9 2024.jpg &amp; A9 2025.jpg)</t>
         </is>
       </c>
-      <c r="H14" s="52" t="inlineStr">
+      <c r="H14" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala/create</t>
         </is>
       </c>
-      <c r="I14" s="52" t="n"/>
-      <c r="J14" s="52" t="n"/>
+      <c r="I14" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J14" s="70" t="inlineStr"/>
       <c r="K14" s="52" t="n"/>
       <c r="L14" s="52" t="n"/>
       <c r="M14" s="52" t="n"/>
@@ -1344,32 +1609,36 @@
       <c r="AB14" s="52" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="52" t="n"/>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="A15" s="60" t="n"/>
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="62" t="inlineStr">
         <is>
           <t>Pelaporan (2024)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="D15" s="63" t="n"/>
+      <c r="E15" s="62" t="inlineStr">
         <is>
           <t>SEKSI B: DUKUNGAN ORGANISASI</t>
         </is>
       </c>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="52" t="inlineStr">
+      <c r="F15" s="63" t="n"/>
+      <c r="G15" s="63" t="n"/>
+      <c r="H15" s="60" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala</t>
         </is>
       </c>
-      <c r="I15" s="52" t="n"/>
-      <c r="J15" s="52" t="inlineStr">
+      <c r="I15" s="60" t="inlineStr">
+        <is>
+          <t>SEKSI B</t>
+        </is>
+      </c>
+      <c r="J15" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">informasi berkala dipublikasikan, informasi </t>
         </is>
@@ -1394,46 +1663,46 @@
       <c r="AB15" s="52" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="52" t="n"/>
-      <c r="B16" s="11" t="n">
+      <c r="A16" s="64" t="n"/>
+      <c r="B16" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="76" t="inlineStr">
         <is>
           <t>Jumlah permohonan informasi yang diminta</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E16" s="74" t="inlineStr">
         <is>
           <t>Petunjuk Operasional Kegiatan (POK) Alokasi Anggaran Khusus PPID PKTJ Tahun 2025</t>
         </is>
       </c>
-      <c r="F16" s="32" t="inlineStr">
+      <c r="F16" s="72" t="inlineStr">
         <is>
           <t>Lembar rincian alokasi anggaran khusus operasional dan pemeliharaan layanan informasi publik dalam DIPA/RKA-KL PKTJ.</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr">
+      <c r="G16" s="77" t="inlineStr">
         <is>
           <t>B1-B4.pdf (Halaman POK Anggaran) (Path: AKIP PKTJ 2025\Indikator B\B1-B4.pdf)</t>
         </is>
       </c>
-      <c r="H16" s="52" t="inlineStr">
+      <c r="H16" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala/create</t>
         </is>
       </c>
-      <c r="I16" s="52" t="n"/>
-      <c r="J16" s="52" t="inlineStr">
-        <is>
-          <t>laporan bulanan agustus dibuat dicapture dibuatkan notadinas ke PPID pelaksana ditempbuskan ke PPID Utama.</t>
-        </is>
-      </c>
+      <c r="I16" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J16" s="70" t="inlineStr"/>
       <c r="K16" s="52" t="n"/>
       <c r="L16" s="52" t="n"/>
       <c r="M16" s="52" t="n"/>
@@ -1454,46 +1723,46 @@
       <c r="AB16" s="52" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="52" t="n"/>
-      <c r="B17" s="11" t="n">
+      <c r="A17" s="64" t="n"/>
+      <c r="B17" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="27" t="inlineStr">
+      <c r="C17" s="76" t="inlineStr">
         <is>
           <t>Waktu yang diperlukan dalam memenuhi setiap permohonan informasi</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="E17" s="74" t="inlineStr">
         <is>
           <t>Laporan Pelaksanaan Kegiatan Layanan PPID PKTJ Tegal</t>
         </is>
       </c>
-      <c r="F17" s="32" t="inlineStr">
+      <c r="F17" s="72" t="inlineStr">
         <is>
           <t>Laporan pertanggungjawaban kegiatan operasional, sosialisasi, dan pemutakhiran data informasi publik.</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="G17" s="77" t="inlineStr">
         <is>
           <t>B1-B4.pdf (Halaman Laporan Kegiatan) (Path: AKIP PKTJ 2025\Indikator B\B1-B4.pdf)</t>
         </is>
       </c>
-      <c r="H17" s="52" t="inlineStr">
+      <c r="H17" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/laporan-layanan</t>
         </is>
       </c>
-      <c r="I17" s="52" t="n"/>
-      <c r="J17" s="52" t="inlineStr">
-        <is>
-          <t>pada form permohonan lewat google form ditambah KTP</t>
-        </is>
-      </c>
+      <c r="I17" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J17" s="70" t="inlineStr"/>
       <c r="K17" s="52" t="n"/>
       <c r="L17" s="52" t="n"/>
       <c r="M17" s="52" t="n"/>
@@ -1514,46 +1783,46 @@
       <c r="AB17" s="52" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="52" t="n"/>
-      <c r="B18" s="11" t="n">
+      <c r="A18" s="64" t="n"/>
+      <c r="B18" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="27" t="inlineStr">
+      <c r="C18" s="76" t="inlineStr">
         <is>
           <t>Jumlah permohonan informasi publik yang dikabulkan baik sebagian atau seluruhnya dan yang ditolak</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="74" t="inlineStr">
         <is>
           <t>SOP dan Alur Koordinasi Penanganan Keberatan dan Sengketa Informasi Publik</t>
         </is>
       </c>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="F18" s="72" t="inlineStr">
         <is>
           <t>Bagan prosedur operasional penanganan pengajuan keberatan dan mediasi/ajudasi sengketa informasi publik.</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr">
+      <c r="G18" s="77" t="inlineStr">
         <is>
           <t>B1-B4.pdf (Halaman Alur Koordinasi) (Path: AKIP PKTJ 2025\Indikator B\B1-B4.pdf)</t>
         </is>
       </c>
-      <c r="H18" s="52" t="inlineStr">
+      <c r="H18" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/prosedur/sop-keberatan</t>
         </is>
       </c>
-      <c r="I18" s="52" t="n"/>
-      <c r="J18" s="52" t="inlineStr">
-        <is>
-          <t>Maklumat PPID dibuat, dicetak, taruh di ruang PPID</t>
-        </is>
-      </c>
+      <c r="I18" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J18" s="70" t="inlineStr"/>
       <c r="K18" s="52" t="n"/>
       <c r="L18" s="52" t="n"/>
       <c r="M18" s="52" t="n"/>
@@ -1574,46 +1843,46 @@
       <c r="AB18" s="52" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="52" t="n"/>
-      <c r="B19" s="11" t="n">
+      <c r="A19" s="64" t="n"/>
+      <c r="B19" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C19" s="76" t="inlineStr">
         <is>
           <t>Alasan penolakan permohonan informasi</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E19" s="74" t="inlineStr">
         <is>
           <t>Surat Rekapitulasi dan Berita Acara Konsolidasi Usulan DIP &amp; DIK PKTJ</t>
         </is>
       </c>
-      <c r="F19" s="32" t="inlineStr">
+      <c r="F19" s="72" t="inlineStr">
         <is>
           <t>Dokumen rekapitulasi usulan klasifikasi informasi terbuka dan dikecualikan dari seluruh unit kerja internal PKTJ.</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr">
+      <c r="G19" s="77" t="inlineStr">
         <is>
           <t>B1-B4.pdf (Halaman Usulan DIP/DIK) (Path: AKIP PKTJ 2025\Indikator B\B1-B4.pdf)</t>
         </is>
       </c>
-      <c r="H19" s="52" t="inlineStr">
+      <c r="H19" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/setiap-saat/create</t>
         </is>
       </c>
-      <c r="I19" s="52" t="n"/>
-      <c r="J19" s="52" t="inlineStr">
-        <is>
-          <t>untuk LSM wajib KTP dan Akta pendirian LSM</t>
-        </is>
-      </c>
+      <c r="I19" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J19" s="70" t="inlineStr"/>
       <c r="K19" s="52" t="n"/>
       <c r="L19" s="52" t="n"/>
       <c r="M19" s="52" t="n"/>
@@ -1634,50 +1903,46 @@
       <c r="AB19" s="52" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="52" t="n"/>
-      <c r="B20" s="11" t="n">
+      <c r="A20" s="64" t="n"/>
+      <c r="B20" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara telah menyampaikan laporan layanan informasi publik tahun 2024 ke PPID Utama?</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="67" t="inlineStr">
         <is>
           <t>Bukti Kehadiran dan Komitmen Pimpinan PKTJ pada Penganugerahan &amp; Monev KIP</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="64" t="inlineStr">
         <is>
           <t>Foto dokumentasi, absensi, dan bukti kehadiran Direktur PKTJ pada penganugerahan AKIP Kemenhub.</t>
         </is>
       </c>
-      <c r="G20" s="29" t="inlineStr">
+      <c r="G20" s="78" t="inlineStr">
         <is>
           <t>B5.pdf / B5.jpeg / B5.png (Path: AKIP PKTJ 2025\Indikator B\B5\B5.pdf)</t>
         </is>
       </c>
-      <c r="H20" s="52" t="inlineStr">
+      <c r="H20" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala/create</t>
         </is>
       </c>
-      <c r="I20" s="52" t="inlineStr">
-        <is>
-          <t>Surat</t>
-        </is>
-      </c>
-      <c r="J20" s="52" t="inlineStr">
-        <is>
-          <t>DIP dan DIK 2025 kemenhub tolong dimasukkan</t>
-        </is>
-      </c>
+      <c r="I20" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J20" s="70" t="inlineStr"/>
       <c r="K20" s="52" t="n"/>
       <c r="L20" s="52" t="n"/>
       <c r="M20" s="52" t="n"/>
@@ -1698,32 +1963,36 @@
       <c r="AB20" s="52" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="52" t="n"/>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="A21" s="60" t="n"/>
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="62" t="inlineStr">
         <is>
           <t>Sarana dan Prasarana</t>
         </is>
       </c>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="D21" s="63" t="n"/>
+      <c r="E21" s="63" t="inlineStr">
         <is>
           <t>SEKSI C: SARANA DAN PRASARANA (11 Poin)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n"/>
-      <c r="H21" s="52" t="inlineStr">
+      <c r="F21" s="63" t="n"/>
+      <c r="G21" s="63" t="n"/>
+      <c r="H21" s="60" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/maklumat-pelayanan</t>
         </is>
       </c>
-      <c r="I21" s="52" t="n"/>
-      <c r="J21" s="52" t="inlineStr">
+      <c r="I21" s="60" t="inlineStr">
+        <is>
+          <t>SEKSI C</t>
+        </is>
+      </c>
+      <c r="J21" s="60" t="inlineStr">
         <is>
           <t>Tujuan permohonan informasi pada google form diberi pilihan: Pengawasan, Kajian, penelitian, keterlibatan, melihat.</t>
         </is>
@@ -1750,42 +2019,46 @@
       <c r="AB21" s="52" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="52" t="n"/>
-      <c r="B22" s="11" t="n">
+      <c r="A22" s="64" t="n"/>
+      <c r="B22" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan Meja Layanan Informasi/PPID?</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="67" t="inlineStr">
         <is>
           <t>Foto Sarana dan Prasarana Ruang Layanan PPID PKTJ Tegal</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="64" t="inlineStr">
         <is>
           <t>Dokumentasi fasilitas meja layanan representatif, komputer akses publik, ruang tunggu, dan banner alur.</t>
         </is>
       </c>
-      <c r="G22" s="39" t="inlineStr">
+      <c r="G22" s="68" t="inlineStr">
         <is>
           <t>C1.png / C2.JPG / DSC06430-6435.JPG (Path: AKIP PKTJ 2025\Indikator C\C1.png &amp; C2.JPG)</t>
         </is>
       </c>
-      <c r="H22" s="52" t="inlineStr">
+      <c r="H22" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/maklumat-pelayanan</t>
         </is>
       </c>
-      <c r="I22" s="52" t="n"/>
-      <c r="J22" s="52" t="n"/>
+      <c r="I22" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J22" s="70" t="inlineStr"/>
       <c r="K22" s="52" t="n"/>
       <c r="L22" s="52" t="n"/>
       <c r="M22" s="52" t="n"/>
@@ -1806,42 +2079,46 @@
       <c r="AB22" s="52" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="52" t="n"/>
-      <c r="B23" s="11" t="n">
+      <c r="A23" s="64" t="n"/>
+      <c r="B23" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan Formulir Permohonan Informasi?</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E23" s="74" t="inlineStr">
         <is>
           <t>Formulir Fisik Permohonan Informasi Publik (Sesuai PM 46 Tahun 2018)</t>
         </is>
       </c>
-      <c r="F23" s="31" t="inlineStr">
+      <c r="F23" s="79" t="inlineStr">
         <is>
           <t>Formulir cetak resmi yang disediakan di meja layanan PPID untuk pemohon luring.</t>
         </is>
       </c>
-      <c r="G23" s="31" t="inlineStr">
+      <c r="G23" s="79" t="inlineStr">
         <is>
           <t>C3.pdf (Path: AKIP PKTJ 2025\Indikator C\C3.pdf)</t>
         </is>
       </c>
-      <c r="H23" s="52" t="inlineStr">
+      <c r="H23" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/prosedur/sop-permintaan</t>
         </is>
       </c>
-      <c r="I23" s="52" t="n"/>
-      <c r="J23" s="52" t="n"/>
+      <c r="I23" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J23" s="70" t="inlineStr"/>
       <c r="K23" s="52" t="n"/>
       <c r="L23" s="52" t="n"/>
       <c r="M23" s="52" t="n"/>
@@ -1862,46 +2139,46 @@
       <c r="AB23" s="52" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="52" t="n"/>
-      <c r="B24" s="11" t="n">
+      <c r="A24" s="64" t="n"/>
+      <c r="B24" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan Daftar Register Permohonan tahun 2024?</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
+      <c r="E24" s="67" t="inlineStr">
         <is>
           <t>Buku Register Pelayanan Permohonan Informasi Publik PKTJ Tahun 2025 (Register NIHIL)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F24" s="64" t="inlineStr">
         <is>
           <t>Buku pencatatan register permohonan informasi masuk bertandatangan pimpinan.</t>
         </is>
       </c>
-      <c r="G24" s="31" t="inlineStr">
+      <c r="G24" s="79" t="inlineStr">
         <is>
           <t>Register_Permohonan_NIHIL.pdf (Path: AKIP PKTJ 2025\Indikator C\Register_Permohonan_NIHIL.pdf)</t>
         </is>
       </c>
-      <c r="H24" s="52" t="inlineStr">
+      <c r="H24" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/laporan-layanan</t>
         </is>
       </c>
-      <c r="I24" s="52" t="n"/>
-      <c r="J24" s="52" t="inlineStr">
-        <is>
-          <t>Tata Cara Permohonan Keberatan Informasi Publik</t>
-        </is>
-      </c>
+      <c r="I24" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J24" s="70" t="inlineStr"/>
       <c r="K24" s="52" t="n"/>
       <c r="L24" s="52" t="n"/>
       <c r="M24" s="52" t="n"/>
@@ -1922,42 +2199,46 @@
       <c r="AB24" s="52" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="52" t="n"/>
-      <c r="B25" s="11" t="n">
+      <c r="A25" s="64" t="n"/>
+      <c r="B25" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengumumkan jadwal pelayanan informasi publik?</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="71" t="inlineStr">
         <is>
           <t>Pigura Maklumat Pelayanan Informasi Publik Bertandatangan Direktur PKTJ</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F25" s="64" t="inlineStr">
         <is>
           <t>Foto pigura maklumat janji layanan informasi yang terpasang di dinding ruang PPID dan tayang di website.</t>
         </is>
       </c>
-      <c r="G25" s="39" t="inlineStr">
+      <c r="G25" s="68" t="inlineStr">
         <is>
           <t>C5.pdf / C5.JPG / C5.png (Path: AKIP PKTJ 2025\Indikator C\C5\C5.pdf)</t>
         </is>
       </c>
-      <c r="H25" s="52" t="inlineStr">
+      <c r="H25" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/maklumat-pelayanan</t>
         </is>
       </c>
-      <c r="I25" s="52" t="n"/>
-      <c r="J25" s="52" t="n"/>
+      <c r="I25" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J25" s="70" t="inlineStr"/>
       <c r="K25" s="52" t="n"/>
       <c r="L25" s="52" t="n"/>
       <c r="M25" s="52" t="n"/>
@@ -1978,46 +2259,46 @@
       <c r="AB25" s="52" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="52" t="n"/>
-      <c r="B26" s="11" t="n">
+      <c r="A26" s="64" t="n"/>
+      <c r="B26" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengumumkan informasi mengenai Maklumat Pelayanan Keterbukaan Informasi Publik?</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr">
+      <c r="E26" s="67" t="inlineStr">
         <is>
           <t>Surat Penetapan Standar Biaya Layanan Informasi Publik (Rp 0 / Bebas Biaya)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F26" s="64" t="inlineStr">
         <is>
           <t>Pengumuman resmi bahwa seluruh pelayanan permohonan informasi publik di PPID PKTJ tidak dipungut biaya.</t>
         </is>
       </c>
-      <c r="G26" s="39" t="inlineStr">
+      <c r="G26" s="68" t="inlineStr">
         <is>
           <t>C6.pdf / C6.JPG / C6.png (Path: AKIP PKTJ 2025\Indikator C\C6\C6.pdf)</t>
         </is>
       </c>
-      <c r="H26" s="52" t="inlineStr">
+      <c r="H26" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/maklumat-pelayanan</t>
         </is>
       </c>
-      <c r="I26" s="52" t="n"/>
-      <c r="J26" s="52" t="inlineStr">
-        <is>
-          <t>Data dimutakhirkan tiap 6 bulan sekali</t>
-        </is>
-      </c>
+      <c r="I26" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J26" s="70" t="inlineStr"/>
       <c r="K26" s="52" t="n"/>
       <c r="L26" s="52" t="n"/>
       <c r="M26" s="52" t="n"/>
@@ -2038,46 +2319,46 @@
       <c r="AB26" s="52" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="52" t="n"/>
-      <c r="B27" s="11" t="n">
+      <c r="A27" s="64" t="n"/>
+      <c r="B27" s="65" t="n">
         <v>6</v>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengumumkan kebijakan mengenai Standar Biaya Perolehan Informasi Publik?</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E27" s="19" t="inlineStr">
+      <c r="E27" s="67" t="inlineStr">
         <is>
           <t>Banner Infografis Tata Cara &amp; Alur Pelayanan Informasi Publik</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F27" s="64" t="inlineStr">
         <is>
           <t>Foto banner/papan alur permohonan informasi yang terpasang jelas di ruang tunggu PPID PKTJ.</t>
         </is>
       </c>
-      <c r="G27" s="39" t="inlineStr">
+      <c r="G27" s="68" t="inlineStr">
         <is>
           <t>Banner_SOP_Layanan.jpg (Path: AKIP PKTJ 2025\Indikator C\Banner_SOP_Layanan.jpg)</t>
         </is>
       </c>
-      <c r="H27" s="52" t="inlineStr">
+      <c r="H27" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/prosedur/sop-permintaan</t>
         </is>
       </c>
-      <c r="I27" s="52" t="n"/>
-      <c r="J27" s="52" t="inlineStr">
-        <is>
-          <t>Laptah UPT dimuat di website, salah satu konten unggulan dimuat jadi konten di medsos</t>
-        </is>
-      </c>
+      <c r="I27" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J27" s="70" t="inlineStr"/>
       <c r="K27" s="52" t="n"/>
       <c r="L27" s="52" t="n"/>
       <c r="M27" s="52" t="n"/>
@@ -2098,43 +2379,47 @@
       <c r="AB27" s="52" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="52" t="n"/>
-      <c r="B28" s="11" t="n">
+      <c r="A28" s="60" t="n"/>
+      <c r="B28" s="61" t="n">
         <v>7</v>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="62" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengumumkan Informasi mengenai tata cara permohonan informasi?</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="63" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="63" t="inlineStr">
         <is>
           <t>SEKSI D: AKSESIBILITAS LAYANAN INFORMASI PUBLIK (13 Poin)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F28" s="63" t="inlineStr">
         <is>
           <t>Di website dan di ruang PPID</t>
         </is>
       </c>
-      <c r="G28" s="32" t="inlineStr">
+      <c r="G28" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">FIXED
 </t>
         </is>
       </c>
-      <c r="H28" s="52" t="inlineStr">
+      <c r="H28" s="60" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/menu</t>
         </is>
       </c>
-      <c r="I28" s="52" t="n"/>
-      <c r="J28" s="52" t="inlineStr">
+      <c r="I28" s="60" t="inlineStr">
+        <is>
+          <t>SEKSI D</t>
+        </is>
+      </c>
+      <c r="J28" s="60" t="inlineStr">
         <is>
           <t>cara membikin konten tentang keuangan, cukup diceritakan pembangunan yg ada diambil dari APBN</t>
         </is>
@@ -2159,42 +2444,46 @@
       <c r="AB28" s="52" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="52" t="n"/>
-      <c r="B29" s="11" t="n">
+      <c r="A29" s="64" t="n"/>
+      <c r="B29" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengumumkan Informasi mengenai tata cara pengajuan keberatan?</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="71" t="inlineStr">
         <is>
           <t>Portal Digital Resmi Mandiri PPID Pelaksana PKTJ Tegal</t>
         </is>
       </c>
-      <c r="F29" s="32" t="inlineStr">
+      <c r="F29" s="72" t="inlineStr">
         <is>
           <t>Tangkapan layar portal web resmi PPID PKTJ (https://pktj.ac.id/ppid) yang terintegrasi dengan subdomain UPT.</t>
         </is>
       </c>
-      <c r="G29" s="32" t="inlineStr">
+      <c r="G29" s="72" t="inlineStr">
         <is>
           <t>D1.pdf (Path: AKIP PKTJ 2025\Indikator D\D1.pdf)</t>
         </is>
       </c>
-      <c r="H29" s="52" t="inlineStr">
+      <c r="H29" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/menu</t>
         </is>
       </c>
-      <c r="I29" s="52" t="n"/>
-      <c r="J29" s="52" t="n"/>
+      <c r="I29" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J29" s="70" t="inlineStr"/>
       <c r="K29" s="52" t="n"/>
       <c r="L29" s="52" t="n"/>
       <c r="M29" s="52" t="n"/>
@@ -2215,42 +2504,46 @@
       <c r="AB29" s="52" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="52" t="n"/>
-      <c r="B30" s="11" t="n">
+      <c r="A30" s="64" t="n"/>
+      <c r="B30" s="65" t="n">
         <v>9</v>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengumumkan Informasi mengenai tata cara pengajuan permohonan penyelesaian sengketa ke Komisi Informasi?</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E30" s="71" t="inlineStr">
         <is>
           <t>Direktori Publikasi 3 Kategori Informasi Publik PPID PKTJ</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="64" t="inlineStr">
         <is>
           <t>Tangkapan layar menu direktori Informasi Berkala, Setiap Saat, dan Serta Merta di website.</t>
         </is>
       </c>
-      <c r="G30" s="39" t="inlineStr">
+      <c r="G30" s="68" t="inlineStr">
         <is>
           <t>D2.pdf / D3.pdf / D4.pdf (Path: AKIP PKTJ 2025\Indikator D\D2.pdf &amp; D3.pdf)</t>
         </is>
       </c>
-      <c r="H30" s="52" t="inlineStr">
+      <c r="H30" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala</t>
         </is>
       </c>
-      <c r="I30" s="52" t="n"/>
-      <c r="J30" s="52" t="n"/>
+      <c r="I30" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J30" s="70" t="inlineStr"/>
       <c r="K30" s="52" t="n"/>
       <c r="L30" s="52" t="n"/>
       <c r="M30" s="52" t="n"/>
@@ -2271,44 +2564,48 @@
       <c r="AB30" s="52" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="52" t="n"/>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="A31" s="64" t="n"/>
+      <c r="B31" s="80" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="81" t="inlineStr">
         <is>
           <t>Aksesibilitas Layanan Informasi Publik</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E31" s="64" t="inlineStr">
         <is>
           <t>Fitur Aksesibilitas Disabilitas &amp; Video Panduan Bahasa Isyarat (Bisindo)</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F31" s="64" t="inlineStr">
         <is>
           <t>Tangkapan layar widget difabel (Kontras Tinggi, Text-to-Speech, Bisindo) dan video panduan ber-subtitle.</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G31" s="64" t="inlineStr">
         <is>
           <t>D5.jpg (Path: AKIP PKTJ 2025\Indikator D\D5.jpg)</t>
         </is>
       </c>
-      <c r="H31" s="52" t="inlineStr">
+      <c r="H31" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/menu</t>
         </is>
       </c>
-      <c r="I31" s="52" t="n"/>
-      <c r="J31" s="52" t="n"/>
+      <c r="I31" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J31" s="70" t="inlineStr"/>
       <c r="K31" s="52" t="n"/>
       <c r="L31" s="52" t="n"/>
       <c r="M31" s="52" t="n"/>
@@ -2329,38 +2626,42 @@
       <c r="AB31" s="52" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="52" t="n"/>
-      <c r="B32" s="11" t="n">
+      <c r="A32" s="60" t="n"/>
+      <c r="B32" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="62" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara memiliki web/laman/menu/direktori khusus PPID/Keterbukaan Informasi Publik/Informasi Publik?</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="63" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E32" s="62" t="inlineStr">
         <is>
           <t>SEKSI E: PELAPORAN (6 Poin)</t>
         </is>
       </c>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="39" t="inlineStr">
+      <c r="F32" s="62" t="n"/>
+      <c r="G32" s="63" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
       </c>
-      <c r="H32" s="52" t="inlineStr">
+      <c r="H32" s="60" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/laporan-layanan</t>
         </is>
       </c>
-      <c r="I32" s="52" t="n"/>
-      <c r="J32" s="52" t="inlineStr">
+      <c r="I32" s="60" t="inlineStr">
+        <is>
+          <t>SEKSI E</t>
+        </is>
+      </c>
+      <c r="J32" s="60" t="inlineStr">
         <is>
           <t>NOMOR 2 MEDIA SOSIAL DIHAPUS
 INFORMASI BERKALA, SERTA MERTA, DLL YG DI DIP BELUM DISESUAIKAN</t>
@@ -2386,42 +2687,46 @@
       <c r="AB32" s="52" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="52" t="n"/>
-      <c r="B33" s="11" t="n">
+      <c r="A33" s="64" t="n"/>
+      <c r="B33" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengumumkan informasi berkala di web/ laman/ menu/ direktori khusus PPID ?</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E33" s="24" t="inlineStr">
+      <c r="E33" s="74" t="inlineStr">
         <is>
           <t>Laporan Rekapitulasi Layanan Informasi Publik PKTJ Tahun 2024-2025</t>
         </is>
       </c>
-      <c r="F33" s="32" t="inlineStr">
+      <c r="F33" s="72" t="inlineStr">
         <is>
           <t>Laporan rinci jumlah pemohon, waktu penyelesaian, dan status pemenuhan informasi publik.</t>
         </is>
       </c>
-      <c r="G33" s="39" t="inlineStr">
+      <c r="G33" s="68" t="inlineStr">
         <is>
           <t>E.1.3.png / E2.pdf / E3.pdf / E4.pdf (Path: AKIP PKTJ 2025\Indikator E\E2.pdf &amp; E3.pdf)</t>
         </is>
       </c>
-      <c r="H33" s="52" t="inlineStr">
+      <c r="H33" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/laporan-layanan</t>
         </is>
       </c>
-      <c r="I33" s="52" t="n"/>
-      <c r="J33" s="52" t="n"/>
+      <c r="I33" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J33" s="70" t="inlineStr"/>
       <c r="K33" s="52" t="n"/>
       <c r="L33" s="52" t="n"/>
       <c r="M33" s="52" t="n"/>
@@ -2442,42 +2747,46 @@
       <c r="AB33" s="52" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="52" t="n"/>
-      <c r="B34" s="11" t="n">
+      <c r="A34" s="64" t="n"/>
+      <c r="B34" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengumumkan informasi setiap saat di web/ laman/ menu/ direktori khusus PPID ?</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E34" s="74" t="inlineStr">
         <is>
           <t>Buku Laporan Tahunan Layanan PPID PKTJ Format PM 46 Tahun 2018</t>
         </is>
       </c>
-      <c r="F34" s="32" t="inlineStr">
+      <c r="F34" s="72" t="inlineStr">
         <is>
           <t>Laporan tahunan resmi PPID UPT lengkap dengan bukti tanda terima pengiriman berjenjang ke BPSDMP.</t>
         </is>
       </c>
-      <c r="G34" s="39" t="inlineStr">
+      <c r="G34" s="68" t="inlineStr">
         <is>
           <t>E6.pdf / E6a.jpg / E6b.jpg / E7.pdf (Path: AKIP PKTJ 2025\Indikator E\E6.pdf &amp; E7.pdf)</t>
         </is>
       </c>
-      <c r="H34" s="52" t="inlineStr">
+      <c r="H34" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/laporan-layanan</t>
         </is>
       </c>
-      <c r="I34" s="52" t="n"/>
-      <c r="J34" s="52" t="n"/>
+      <c r="I34" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J34" s="70" t="inlineStr"/>
       <c r="K34" s="52" t="n"/>
       <c r="L34" s="52" t="n"/>
       <c r="M34" s="52" t="n"/>
@@ -2498,38 +2807,42 @@
       <c r="AB34" s="52" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="52" t="n"/>
-      <c r="B35" s="11" t="n">
+      <c r="A35" s="60" t="n"/>
+      <c r="B35" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="C35" s="27" t="inlineStr">
+      <c r="C35" s="62" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengumumkan informasi serta merta di web/ laman/ menu/ direktori khusus PPID ?</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="63" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E35" s="62" t="inlineStr">
         <is>
           <t>SEKSI F: INFORMASI BERKALA &amp; PENGADAAN BARANG JASA (43,5 Poin)</t>
         </is>
       </c>
-      <c r="F35" s="32" t="n"/>
-      <c r="G35" s="39" t="inlineStr">
+      <c r="F35" s="62" t="n"/>
+      <c r="G35" s="63" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
       </c>
-      <c r="H35" s="52" t="inlineStr">
+      <c r="H35" s="60" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala</t>
         </is>
       </c>
-      <c r="I35" s="52" t="n"/>
-      <c r="J35" s="52" t="n"/>
+      <c r="I35" s="60" t="inlineStr">
+        <is>
+          <t>SEKSI F</t>
+        </is>
+      </c>
+      <c r="J35" s="60" t="n"/>
       <c r="K35" s="52" t="n"/>
       <c r="L35" s="52" t="n"/>
       <c r="M35" s="52" t="n"/>
@@ -2550,42 +2863,46 @@
       <c r="AB35" s="52" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="52" t="n"/>
-      <c r="B36" s="11" t="n">
+      <c r="A36" s="64" t="n"/>
+      <c r="B36" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara memiliki akses/penunjuk yang memberikan keramahan pada penyandang disabilitas?</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E36" s="19" t="inlineStr">
+      <c r="E36" s="67" t="inlineStr">
         <is>
           <t>Profil Unit Kerja Politeknik Keselamatan Transportasi Jalan (PKTJ) Tegal</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F36" s="64" t="inlineStr">
         <is>
           <t>Informasi kedudukan, domisili, kontak, tugas dan fungsi, struktur organisasi, dan sejarah kampus PKTJ.</t>
         </is>
       </c>
-      <c r="G36" s="39" t="inlineStr">
+      <c r="G36" s="68" t="inlineStr">
         <is>
           <t>F1.pdf (Path: AKIP PKTJ 2025\Indikator F\F1.pdf)</t>
         </is>
       </c>
-      <c r="H36" s="52" t="inlineStr">
+      <c r="H36" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala/create</t>
         </is>
       </c>
-      <c r="I36" s="52" t="n"/>
-      <c r="J36" s="52" t="n"/>
+      <c r="I36" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J36" s="70" t="inlineStr"/>
       <c r="K36" s="52" t="n"/>
       <c r="L36" s="52" t="n"/>
       <c r="M36" s="52" t="n"/>
@@ -2606,44 +2923,48 @@
       <c r="AB36" s="52" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="52" t="n"/>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="A37" s="64" t="n"/>
+      <c r="B37" s="80" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C37" s="81" t="inlineStr">
         <is>
           <t>Informasi Berkala</t>
         </is>
       </c>
-      <c r="D37" s="35" t="inlineStr">
+      <c r="D37" s="82" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="64" t="inlineStr">
         <is>
           <t>Profil Pimpinan &amp; Lembar Berita Negara Pengumuman LHKPN KPK Direktur PKTJ</t>
         </is>
       </c>
-      <c r="F37" s="34" t="inlineStr">
+      <c r="F37" s="83" t="inlineStr">
         <is>
           <t>Profil lengkap pimpinan dan bukti tanda terima LHKPN resmi yang telah diverifikasi KPK.</t>
         </is>
       </c>
-      <c r="G37" s="35" t="inlineStr">
+      <c r="G37" s="82" t="inlineStr">
         <is>
           <t>F2.pdf (Path: AKIP PKTJ 2025\Indikator F\F2.pdf)</t>
         </is>
       </c>
-      <c r="H37" s="52" t="inlineStr">
+      <c r="H37" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala/create</t>
         </is>
       </c>
-      <c r="I37" s="52" t="n"/>
-      <c r="J37" s="52" t="n"/>
+      <c r="I37" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J37" s="70" t="inlineStr"/>
       <c r="K37" s="52" t="n"/>
       <c r="L37" s="52" t="n"/>
       <c r="M37" s="52" t="n"/>
@@ -2664,42 +2985,46 @@
       <c r="AB37" s="52" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="52" t="n"/>
-      <c r="B38" s="11" t="n">
+      <c r="A38" s="64" t="n"/>
+      <c r="B38" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengumumkan profil unit kerja?</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E38" s="71" t="inlineStr">
         <is>
           <t>Laporan Tahunan Akuntabilitas Kinerja Instansi Pemerintah (LAKIP) PKTJ Tahun 2024-2025</t>
         </is>
       </c>
-      <c r="F38" s="32" t="inlineStr">
+      <c r="F38" s="72" t="inlineStr">
         <is>
           <t>Laporan pertanggungjawaban capaian target kinerja tahunan institusi PKTJ Tegal.</t>
         </is>
       </c>
-      <c r="G38" s="39" t="inlineStr">
+      <c r="G38" s="68" t="inlineStr">
         <is>
           <t>F3.xlsx / Laptah_PKTJ.pdf (Path: AKIP PKTJ 2025\Indikator F\F3.xlsx)</t>
         </is>
       </c>
-      <c r="H38" s="52" t="inlineStr">
+      <c r="H38" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala/create</t>
         </is>
       </c>
-      <c r="I38" s="52" t="n"/>
-      <c r="J38" s="52" t="n"/>
+      <c r="I38" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J38" s="70" t="inlineStr"/>
       <c r="K38" s="52" t="n"/>
       <c r="L38" s="52" t="n"/>
       <c r="M38" s="52" t="n"/>
@@ -2720,42 +3045,46 @@
       <c r="AB38" s="52" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="52" t="n"/>
-      <c r="B39" s="36" t="n">
+      <c r="A39" s="64" t="n"/>
+      <c r="B39" s="84" t="n">
         <v>45658</v>
       </c>
-      <c r="C39" s="27" t="inlineStr">
+      <c r="C39" s="76" t="inlineStr">
         <is>
           <t>Alamat kantor lengkap unit kerja (bukan alamat kantor PPID)</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D39" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E39" s="37" t="inlineStr">
+      <c r="E39" s="85" t="inlineStr">
         <is>
           <t>Rencana Kerja dan Anggaran Kementerian/Lembaga (RKA-KL) PKTJ Tahun Anggaran 2025/2026</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F39" s="64" t="inlineStr">
         <is>
           <t>Dokumen perencanaan alokasi program dan anggaran belanja PKTJ.</t>
         </is>
       </c>
-      <c r="G39" s="39" t="inlineStr">
+      <c r="G39" s="68" t="inlineStr">
         <is>
           <t>F4.pdf (Path: AKIP PKTJ 2025\Indikator F\F4.pdf)</t>
         </is>
       </c>
-      <c r="H39" s="52" t="inlineStr">
+      <c r="H39" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala/create</t>
         </is>
       </c>
-      <c r="I39" s="52" t="n"/>
-      <c r="J39" s="52" t="n"/>
+      <c r="I39" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J39" s="70" t="inlineStr"/>
       <c r="K39" s="52" t="n"/>
       <c r="L39" s="52" t="n"/>
       <c r="M39" s="52" t="n"/>
@@ -2776,42 +3105,46 @@
       <c r="AB39" s="52" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="52" t="n"/>
-      <c r="B40" s="36" t="n">
+      <c r="A40" s="64" t="n"/>
+      <c r="B40" s="84" t="n">
         <v>45689</v>
       </c>
-      <c r="C40" s="27" t="inlineStr">
+      <c r="C40" s="76" t="inlineStr">
         <is>
           <t>Tugas Fungsi</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E40" s="19" t="inlineStr">
+      <c r="E40" s="67" t="inlineStr">
         <is>
           <t>Kanal Aduan Pelayanan Publik SP4N-LAPOR! dan Whistleblowing System (WBS) Kemenhub</t>
         </is>
       </c>
-      <c r="F40" s="38" t="inlineStr">
+      <c r="F40" s="86" t="inlineStr">
         <is>
           <t>Publikasi portal aduan terintegrasi nasional www.lapor.go.id dan WBS Kemenhub.</t>
         </is>
       </c>
-      <c r="G40" s="39" t="inlineStr">
+      <c r="G40" s="68" t="inlineStr">
         <is>
           <t>Banner_SP4N_LAPOR_WBS.png (Path: Tayang di Halaman Publik: /informasi-publik/berkala)</t>
         </is>
       </c>
-      <c r="H40" s="52" t="inlineStr">
+      <c r="H40" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala</t>
         </is>
       </c>
-      <c r="I40" s="52" t="n"/>
-      <c r="J40" s="52" t="n"/>
+      <c r="I40" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J40" s="70" t="inlineStr"/>
       <c r="K40" s="52" t="n"/>
       <c r="L40" s="52" t="n"/>
       <c r="M40" s="52" t="n"/>
@@ -2832,42 +3165,46 @@
       <c r="AB40" s="52" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="52" t="n"/>
-      <c r="B41" s="36" t="n">
+      <c r="A41" s="64" t="n"/>
+      <c r="B41" s="84" t="n">
         <v>45717</v>
       </c>
-      <c r="C41" s="27" t="inlineStr">
+      <c r="C41" s="76" t="inlineStr">
         <is>
           <t>Struktur Organisasi</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E41" s="24" t="inlineStr">
+      <c r="E41" s="74" t="inlineStr">
         <is>
           <t>Laporan Keuangan PKTJ Tegal Tahun 2024/2025 (Audited BPK RI)</t>
         </is>
       </c>
-      <c r="F41" s="38" t="inlineStr">
+      <c r="F41" s="86" t="inlineStr">
         <is>
           <t>Laporan pertanggungjawaban posisi keuangan audited: Neraca, LRA, LO, LPE, dan CaLK.</t>
         </is>
       </c>
-      <c r="G41" s="39" t="inlineStr">
+      <c r="G41" s="68" t="inlineStr">
         <is>
           <t>F6.pdf (Path: AKIP PKTJ 2025\Indikator F\F6.pdf)</t>
         </is>
       </c>
-      <c r="H41" s="52" t="inlineStr">
+      <c r="H41" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala/create</t>
         </is>
       </c>
-      <c r="I41" s="52" t="n"/>
-      <c r="J41" s="52" t="n"/>
+      <c r="I41" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J41" s="70" t="inlineStr"/>
       <c r="K41" s="52" t="n"/>
       <c r="L41" s="52" t="n"/>
       <c r="M41" s="52" t="n"/>
@@ -2888,42 +3225,46 @@
       <c r="AB41" s="52" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="52" t="n"/>
-      <c r="B42" s="11" t="n">
+      <c r="A42" s="64" t="n"/>
+      <c r="B42" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengumumkan lembar berita negara Laporan Harta Kekayaan Pejabat Negara (LHKPN) pimpinan unit kerja?</t>
         </is>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D42" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E42" s="40" t="inlineStr">
+      <c r="E42" s="87" t="inlineStr">
         <is>
           <t>Daftar Isian Pelaksanaan Anggaran (DIPA) Induk PKTJ Tahun Anggaran 2025</t>
         </is>
       </c>
-      <c r="F42" s="38" t="inlineStr">
+      <c r="F42" s="86" t="inlineStr">
         <is>
           <t>Dokumen otorisasi pelaksanaan anggaran belanja pemerintah resmi di lingkungan PKTJ Tegal.</t>
         </is>
       </c>
-      <c r="G42" s="41" t="inlineStr">
+      <c r="G42" s="88" t="inlineStr">
         <is>
           <t>F7.pdf (Path: AKIP PKTJ 2025\Indikator F\F7.pdf)</t>
         </is>
       </c>
-      <c r="H42" s="52" t="inlineStr">
+      <c r="H42" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala/create</t>
         </is>
       </c>
-      <c r="I42" s="52" t="n"/>
-      <c r="J42" s="52" t="n"/>
+      <c r="I42" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J42" s="70" t="inlineStr"/>
       <c r="K42" s="52" t="n"/>
       <c r="L42" s="52" t="n"/>
       <c r="M42" s="52" t="n"/>
@@ -2944,42 +3285,46 @@
       <c r="AB42" s="52" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="52" t="n"/>
-      <c r="B43" s="11" t="n">
+      <c r="A43" s="64" t="n"/>
+      <c r="B43" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="66" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengumumkan laporan tahunan 2024?</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D43" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E43" s="24" t="inlineStr">
+      <c r="E43" s="74" t="inlineStr">
         <is>
           <t>Statistik Data Kepegawaian &amp; Sumber Daya Manusia PKTJ Tegal</t>
         </is>
       </c>
-      <c r="F43" s="16" t="inlineStr">
+      <c r="F43" s="64" t="inlineStr">
         <is>
           <t>Diagram statistik profil pegawai berdasarkan jenjang pendidikan, golongan, gender, dan formasi jabatan.</t>
         </is>
       </c>
-      <c r="G43" s="37" t="inlineStr">
+      <c r="G43" s="85" t="inlineStr">
         <is>
           <t>F8.xlsx / Chart_Kepegawaian.png (Path: AKIP PKTJ 2025\Indikator F\F8.xlsx)</t>
         </is>
       </c>
-      <c r="H43" s="52" t="inlineStr">
+      <c r="H43" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala</t>
         </is>
       </c>
-      <c r="I43" s="52" t="n"/>
-      <c r="J43" s="52" t="n"/>
+      <c r="I43" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J43" s="70" t="inlineStr"/>
       <c r="K43" s="52" t="n"/>
       <c r="L43" s="52" t="n"/>
       <c r="M43" s="52" t="n"/>
@@ -3000,42 +3345,46 @@
       <c r="AB43" s="52" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="52" t="n"/>
-      <c r="B44" s="11" t="n">
+      <c r="A44" s="64" t="n"/>
+      <c r="B44" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="C44" s="42" t="inlineStr">
+      <c r="C44" s="89" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengumumkan rencana kerja anggaran tahun 2025?</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D44" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E44" s="19" t="inlineStr">
+      <c r="E44" s="67" t="inlineStr">
         <is>
           <t>Rekapitulasi Profil Tenaga Honorer, Outsourcing, dan PPPK PKTJ Tegal</t>
         </is>
       </c>
-      <c r="F44" s="32" t="inlineStr">
+      <c r="F44" s="72" t="inlineStr">
         <is>
           <t>Data statistik ketenagakerjaan penunjang layanan operasional kampus PKTJ.</t>
         </is>
       </c>
-      <c r="G44" s="41" t="inlineStr">
+      <c r="G44" s="88" t="inlineStr">
         <is>
           <t>F9.xlsx (Path: AKIP PKTJ 2025\Indikator F\F9.xlsx)</t>
         </is>
       </c>
-      <c r="H44" s="52" t="inlineStr">
+      <c r="H44" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/berkala/create</t>
         </is>
       </c>
-      <c r="I44" s="52" t="n"/>
-      <c r="J44" s="52" t="n"/>
+      <c r="I44" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J44" s="70" t="inlineStr"/>
       <c r="K44" s="52" t="n"/>
       <c r="L44" s="52" t="n"/>
       <c r="M44" s="52" t="n"/>
@@ -3209,44 +3558,48 @@
       <c r="AB47" s="52" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="52" t="n"/>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="A48" s="64" t="n"/>
+      <c r="B48" s="80" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="C48" s="44" t="inlineStr">
+      <c r="C48" s="90" t="inlineStr">
         <is>
           <t>INFORMASI BERKALA - DOKUMEN PENGADAAN BARANG DAN JASA</t>
         </is>
       </c>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="D48" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="E48" s="64" t="inlineStr">
         <is>
           <t>Dokumen Rencana Umum Pengadaan (RUP) Paket Pekerjaan PKTJ</t>
         </is>
       </c>
-      <c r="F48" s="16" t="inlineStr">
+      <c r="F48" s="64" t="inlineStr">
         <is>
           <t>Pengumuman paket pengadaan barang/jasa melalui sistem SiRUP LKPP.</t>
         </is>
       </c>
-      <c r="G48" s="16" t="inlineStr">
+      <c r="G48" s="64" t="inlineStr">
         <is>
           <t>F12.pdf (Halaman RUP) (Path: AKIP PKTJ 2025\Indikator F\F12.pdf)</t>
         </is>
       </c>
-      <c r="H48" s="52" t="inlineStr">
+      <c r="H48" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I48" s="52" t="n"/>
-      <c r="J48" s="52" t="n"/>
+      <c r="I48" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J48" s="70" t="inlineStr"/>
       <c r="K48" s="52" t="n"/>
       <c r="L48" s="52" t="n"/>
       <c r="M48" s="52" t="n"/>
@@ -3267,42 +3620,46 @@
       <c r="AB48" s="52" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="52" t="n"/>
-      <c r="B49" s="11" t="n">
+      <c r="A49" s="64" t="n"/>
+      <c r="B49" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="C49" s="45" t="inlineStr">
+      <c r="C49" s="91" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Rencana Umum Pengadaan (RUP) ?</t>
         </is>
       </c>
-      <c r="D49" s="16" t="inlineStr">
+      <c r="D49" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E49" s="21" t="inlineStr">
+      <c r="E49" s="71" t="inlineStr">
         <is>
           <t>Dokumen Kerangka Acuan Kerja (KAK / TOR) Paket Pekerjaan</t>
         </is>
       </c>
-      <c r="F49" s="16" t="inlineStr">
+      <c r="F49" s="64" t="inlineStr">
         <is>
           <t>Ruang lingkup, sasaran, dan keluaran yang dipersyaratkan dalam pengadaan.</t>
         </is>
       </c>
-      <c r="G49" s="41" t="inlineStr">
+      <c r="G49" s="88" t="inlineStr">
         <is>
           <t>F12.pdf (Halaman KAK) (Path: AKIP PKTJ 2025\Indikator F\F12.pdf)</t>
         </is>
       </c>
-      <c r="H49" s="52" t="inlineStr">
+      <c r="H49" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I49" s="52" t="n"/>
-      <c r="J49" s="52" t="n"/>
+      <c r="I49" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J49" s="70" t="inlineStr"/>
       <c r="K49" s="52" t="n"/>
       <c r="L49" s="52" t="n"/>
       <c r="M49" s="52" t="n"/>
@@ -3323,42 +3680,46 @@
       <c r="AB49" s="52" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="52" t="n"/>
-      <c r="B50" s="11" t="n">
+      <c r="A50" s="64" t="n"/>
+      <c r="B50" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="43" t="inlineStr">
+      <c r="C50" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Kerangka Acuan Kerja (KAK) ?</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E50" s="37" t="inlineStr">
+      <c r="E50" s="85" t="inlineStr">
         <is>
           <t>Dokumen Harga Perkiraan Sendiri (HPS) dan Riwayat Penyusunan HPS</t>
         </is>
       </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="F50" s="64" t="inlineStr">
         <is>
           <t>Kalkulasi batas atas harga pengadaan yang telah diaudit dan disahkan PPK.</t>
         </is>
       </c>
-      <c r="G50" s="41" t="inlineStr">
+      <c r="G50" s="88" t="inlineStr">
         <is>
           <t>F12.pdf (Halaman HPS) (Path: AKIP PKTJ 2025\Indikator F\F12.pdf)</t>
         </is>
       </c>
-      <c r="H50" s="52" t="inlineStr">
+      <c r="H50" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I50" s="52" t="n"/>
-      <c r="J50" s="52" t="n"/>
+      <c r="I50" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J50" s="70" t="inlineStr"/>
       <c r="K50" s="52" t="n"/>
       <c r="L50" s="52" t="n"/>
       <c r="M50" s="52" t="n"/>
@@ -3379,42 +3740,46 @@
       <c r="AB50" s="52" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="52" t="n"/>
-      <c r="B51" s="11" t="n">
+      <c r="A51" s="64" t="n"/>
+      <c r="B51" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="C51" s="45" t="inlineStr">
+      <c r="C51" s="91" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Harga Perkiraan Sendiri (HPS) serta Riwayat HPS ?</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D51" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E51" s="37" t="inlineStr">
+      <c r="E51" s="85" t="inlineStr">
         <is>
           <t>Dokumen Spesifikasi Teknis (Spektek) Pengadaan Barang dan Jasa</t>
         </is>
       </c>
-      <c r="F51" s="16" t="inlineStr">
+      <c r="F51" s="64" t="inlineStr">
         <is>
           <t>Uraian teknis, standar mutu, dan merek referensi pekerjaan yang dipersyaratkan.</t>
         </is>
       </c>
-      <c r="G51" s="16" t="inlineStr">
+      <c r="G51" s="64" t="inlineStr">
         <is>
           <t>F12.pdf (Halaman Spektek) (Path: AKIP PKTJ 2025\Indikator F\F12.pdf)</t>
         </is>
       </c>
-      <c r="H51" s="52" t="inlineStr">
+      <c r="H51" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I51" s="52" t="n"/>
-      <c r="J51" s="52" t="n"/>
+      <c r="I51" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J51" s="70" t="inlineStr"/>
       <c r="K51" s="52" t="n"/>
       <c r="L51" s="52" t="n"/>
       <c r="M51" s="52" t="n"/>
@@ -3435,42 +3800,46 @@
       <c r="AB51" s="52" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="52" t="n"/>
-      <c r="B52" s="11" t="n">
+      <c r="A52" s="64" t="n"/>
+      <c r="B52" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="C52" s="43" t="inlineStr">
+      <c r="C52" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Spesifikasi Teknis ?</t>
         </is>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D52" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E52" s="37" t="inlineStr">
+      <c r="E52" s="85" t="inlineStr">
         <is>
           <t>Dokumen Rancangan Surat Perjanjian Kontrak Pengadaan</t>
         </is>
       </c>
-      <c r="F52" s="16" t="inlineStr">
+      <c r="F52" s="64" t="inlineStr">
         <is>
           <t>Draft klausul perjanjian kontrak kerja sama pengadaan barang/jasa.</t>
         </is>
       </c>
-      <c r="G52" s="16" t="inlineStr">
+      <c r="G52" s="64" t="inlineStr">
         <is>
           <t>F12.pdf (Halaman Rancangan Kontrak) (Path: AKIP PKTJ 2025\Indikator F\F12.pdf)</t>
         </is>
       </c>
-      <c r="H52" s="52" t="inlineStr">
+      <c r="H52" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I52" s="52" t="n"/>
-      <c r="J52" s="52" t="n"/>
+      <c r="I52" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J52" s="70" t="inlineStr"/>
       <c r="K52" s="52" t="n"/>
       <c r="L52" s="52" t="n"/>
       <c r="M52" s="52" t="n"/>
@@ -3491,46 +3860,46 @@
       <c r="AB52" s="52" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="52" t="n"/>
-      <c r="B53" s="11" t="n">
+      <c r="A53" s="64" t="n"/>
+      <c r="B53" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="C53" s="43" t="inlineStr">
+      <c r="C53" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Rancangan Kontrak ?</t>
         </is>
       </c>
-      <c r="D53" s="16" t="inlineStr">
+      <c r="D53" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E53" s="21" t="inlineStr">
+      <c r="E53" s="71" t="inlineStr">
         <is>
           <t>Dokumen Lembar Data Kualifikasi (LDK) Persyaratan Penyedia</t>
         </is>
       </c>
-      <c r="F53" s="16" t="inlineStr">
+      <c r="F53" s="64" t="inlineStr">
         <is>
           <t>Syarat legalitas, kualifikasi izin usaha, dan finansial calon penyedia.</t>
         </is>
       </c>
-      <c r="G53" s="37" t="inlineStr">
+      <c r="G53" s="85" t="inlineStr">
         <is>
           <t>F12.pdf (Halaman LDK) (Path: AKIP PKTJ 2025\Indikator F\F12.pdf)</t>
         </is>
       </c>
-      <c r="H53" s="52" t="inlineStr">
+      <c r="H53" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I53" s="52" t="n"/>
-      <c r="J53" s="52" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="I53" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J53" s="70" t="inlineStr"/>
       <c r="K53" s="52" t="n"/>
       <c r="L53" s="52" t="n"/>
       <c r="M53" s="52" t="n"/>
@@ -3551,42 +3920,46 @@
       <c r="AB53" s="52" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="52" t="n"/>
-      <c r="B54" s="11" t="n">
+      <c r="A54" s="64" t="n"/>
+      <c r="B54" s="65" t="n">
         <v>6</v>
       </c>
-      <c r="C54" s="43" t="inlineStr">
+      <c r="C54" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Dokumen Persyaratan Penyedia atau Lembar Data Kualifikasi ?</t>
         </is>
       </c>
-      <c r="D54" s="16" t="inlineStr">
+      <c r="D54" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E54" s="37" t="inlineStr">
+      <c r="E54" s="85" t="inlineStr">
         <is>
           <t>Dokumen Lembar Data Pemilihan (LDP) Paket Pekerjaan</t>
         </is>
       </c>
-      <c r="F54" s="16" t="inlineStr">
+      <c r="F54" s="64" t="inlineStr">
         <is>
           <t>Tata cara evaluasi penawaran dan pembobotan teknis pengadaan.</t>
         </is>
       </c>
-      <c r="G54" s="16" t="inlineStr">
+      <c r="G54" s="64" t="inlineStr">
         <is>
           <t>F12.pdf (Halaman LDP) (Path: AKIP PKTJ 2025\Indikator F\F12.pdf)</t>
         </is>
       </c>
-      <c r="H54" s="52" t="inlineStr">
+      <c r="H54" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I54" s="52" t="n"/>
-      <c r="J54" s="52" t="n"/>
+      <c r="I54" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J54" s="70" t="inlineStr"/>
       <c r="K54" s="52" t="n"/>
       <c r="L54" s="52" t="n"/>
       <c r="M54" s="52" t="n"/>
@@ -3607,42 +3980,46 @@
       <c r="AB54" s="52" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="52" t="n"/>
-      <c r="B55" s="11" t="n">
+      <c r="A55" s="64" t="n"/>
+      <c r="B55" s="65" t="n">
         <v>7</v>
       </c>
-      <c r="C55" s="43" t="inlineStr">
+      <c r="C55" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Dokumen Persyaratan Proses Pemilihan atau Lembar Data Pemilihan ?</t>
         </is>
       </c>
-      <c r="D55" s="16" t="inlineStr">
+      <c r="D55" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E55" s="37" t="inlineStr">
+      <c r="E55" s="85" t="inlineStr">
         <is>
           <t>Dokumen Daftar Kuantitas dan Harga (Bill of Quantity)</t>
         </is>
       </c>
-      <c r="F55" s="16" t="inlineStr">
+      <c r="F55" s="64" t="inlineStr">
         <is>
           <t>Rincian item volume dan satuan harga penawaran pekerjaan.</t>
         </is>
       </c>
-      <c r="G55" s="16" t="inlineStr">
+      <c r="G55" s="64" t="inlineStr">
         <is>
           <t>F12.pdf (Halaman BoQ) (Path: AKIP PKTJ 2025\Indikator F\F12.pdf)</t>
         </is>
       </c>
-      <c r="H55" s="52" t="inlineStr">
+      <c r="H55" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I55" s="52" t="n"/>
-      <c r="J55" s="52" t="n"/>
+      <c r="I55" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J55" s="70" t="inlineStr"/>
       <c r="K55" s="52" t="n"/>
       <c r="L55" s="52" t="n"/>
       <c r="M55" s="52" t="n"/>
@@ -3663,42 +4040,46 @@
       <c r="AB55" s="52" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="52" t="n"/>
-      <c r="B56" s="11" t="n">
+      <c r="A56" s="64" t="n"/>
+      <c r="B56" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="C56" s="43" t="inlineStr">
+      <c r="C56" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Daftar Kuantitas dan Harga ?</t>
         </is>
       </c>
-      <c r="D56" s="16" t="inlineStr">
+      <c r="D56" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E56" s="37" t="inlineStr">
+      <c r="E56" s="85" t="inlineStr">
         <is>
           <t>Dokumen Jadwal Tahapan Pelaksanaan &amp; Titik Lokasi Pekerjaan</t>
         </is>
       </c>
-      <c r="F56" s="16" t="inlineStr">
+      <c r="F56" s="64" t="inlineStr">
         <is>
           <t>Time schedule kurva S dan titik lokasi kampus pelaksanaan pekerjaan.</t>
         </is>
       </c>
-      <c r="G56" s="16" t="inlineStr">
+      <c r="G56" s="64" t="inlineStr">
         <is>
           <t>F12.pdf (Halaman Jadwal/Lokasi) (Path: AKIP PKTJ 2025\Indikator F\F12.pdf)</t>
         </is>
       </c>
-      <c r="H56" s="52" t="inlineStr">
+      <c r="H56" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I56" s="52" t="n"/>
-      <c r="J56" s="52" t="n"/>
+      <c r="I56" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J56" s="70" t="inlineStr"/>
       <c r="K56" s="52" t="n"/>
       <c r="L56" s="52" t="n"/>
       <c r="M56" s="52" t="n"/>
@@ -3719,42 +4100,46 @@
       <c r="AB56" s="52" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="52" t="n"/>
-      <c r="B57" s="11" t="n">
+      <c r="A57" s="64" t="n"/>
+      <c r="B57" s="65" t="n">
         <v>9</v>
       </c>
-      <c r="C57" s="43" t="inlineStr">
+      <c r="C57" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Jadwal pelaksanaan dan data lokasi pekerjaan ?</t>
         </is>
       </c>
-      <c r="D57" s="16" t="inlineStr">
+      <c r="D57" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E57" s="37" t="inlineStr">
+      <c r="E57" s="85" t="inlineStr">
         <is>
           <t>Gambar Rancangan Teknis dan Desain Konstruksi Pekerjaan</t>
         </is>
       </c>
-      <c r="F57" s="16" t="inlineStr">
+      <c r="F57" s="64" t="inlineStr">
         <is>
           <t>Gambar teknis denah dan spesifikasi visual konstruksi.</t>
         </is>
       </c>
-      <c r="G57" s="43" t="inlineStr">
+      <c r="G57" s="92" t="inlineStr">
         <is>
           <t>F12.pdf (Halaman Gambar Rancang) (Path: AKIP PKTJ 2025\Indikator F\F12.pdf)</t>
         </is>
       </c>
-      <c r="H57" s="52" t="inlineStr">
+      <c r="H57" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I57" s="52" t="n"/>
-      <c r="J57" s="52" t="n"/>
+      <c r="I57" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J57" s="70" t="inlineStr"/>
       <c r="K57" s="52" t="n"/>
       <c r="L57" s="52" t="n"/>
       <c r="M57" s="52" t="n"/>
@@ -3775,46 +4160,46 @@
       <c r="AB57" s="52" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="52" t="n"/>
-      <c r="B58" s="11" t="n">
+      <c r="A58" s="64" t="n"/>
+      <c r="B58" s="65" t="n">
         <v>10</v>
       </c>
-      <c r="C58" s="43" t="inlineStr">
+      <c r="C58" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Gambar Rancangan Pekerjaan ?</t>
         </is>
       </c>
-      <c r="D58" s="16" t="inlineStr">
+      <c r="D58" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E58" s="21" t="inlineStr">
+      <c r="E58" s="71" t="inlineStr">
         <is>
           <t>Dokumen Pengelolaan Lingkungan Hidup (UKL-UPL / AMDAL)</t>
         </is>
       </c>
-      <c r="F58" s="16" t="inlineStr">
+      <c r="F58" s="64" t="inlineStr">
         <is>
           <t>Analisis dampak lingkungan dan izin kepatuhan lingkungan kampus.</t>
         </is>
       </c>
-      <c r="G58" s="37" t="inlineStr">
+      <c r="G58" s="85" t="inlineStr">
         <is>
           <t>F12.pdf (Halaman Lingkungan) (Path: AKIP PKTJ 2025\Indikator F\F12.pdf)</t>
         </is>
       </c>
-      <c r="H58" s="52" t="inlineStr">
+      <c r="H58" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I58" s="52" t="n"/>
-      <c r="J58" s="52" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="I58" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J58" s="70" t="inlineStr"/>
       <c r="K58" s="52" t="n"/>
       <c r="L58" s="52" t="n"/>
       <c r="M58" s="52" t="n"/>
@@ -3835,42 +4220,46 @@
       <c r="AB58" s="52" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="52" t="n"/>
-      <c r="B59" s="11" t="n">
+      <c r="A59" s="64" t="n"/>
+      <c r="B59" s="65" t="n">
         <v>11</v>
       </c>
-      <c r="C59" s="43" t="inlineStr">
+      <c r="C59" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Dokumen Studi Kelayakan dan Dokumen Lingkungan Hidup, termasuk Analisis Mengenai Dampak Lingkungan ?</t>
         </is>
       </c>
-      <c r="D59" s="16" t="inlineStr">
+      <c r="D59" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E59" s="16" t="inlineStr">
+      <c r="E59" s="64" t="inlineStr">
         <is>
           <t>Dokumen Penawaran Administratif Penyedia Barang dan Jasa</t>
         </is>
       </c>
-      <c r="F59" s="16" t="inlineStr">
+      <c r="F59" s="64" t="inlineStr">
         <is>
           <t>Surat penawaran dan kelengkapan berkas administrasi penyedia.</t>
         </is>
       </c>
-      <c r="G59" s="37" t="inlineStr">
+      <c r="G59" s="85" t="inlineStr">
         <is>
           <t>F12.pdf (Halaman Penawaran) (Path: AKIP PKTJ 2025\Indikator F\F12.pdf)</t>
         </is>
       </c>
-      <c r="H59" s="52" t="inlineStr">
+      <c r="H59" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I59" s="52" t="n"/>
-      <c r="J59" s="52" t="n"/>
+      <c r="I59" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J59" s="70" t="inlineStr"/>
       <c r="K59" s="52" t="n"/>
       <c r="L59" s="52" t="n"/>
       <c r="M59" s="52" t="n"/>
@@ -3891,42 +4280,46 @@
       <c r="AB59" s="52" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="52" t="n"/>
-      <c r="B60" s="11" t="n">
+      <c r="A60" s="64" t="n"/>
+      <c r="B60" s="65" t="n">
         <v>12</v>
       </c>
-      <c r="C60" s="43" t="inlineStr">
+      <c r="C60" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Dokumen Penawaran Administratif ?</t>
         </is>
       </c>
-      <c r="D60" s="16" t="inlineStr">
+      <c r="D60" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E60" s="37" t="inlineStr">
+      <c r="E60" s="85" t="inlineStr">
         <is>
           <t>Surat Penawaran Harga Resmi dari Penyedia Barang dan Jasa</t>
         </is>
       </c>
-      <c r="F60" s="16" t="inlineStr">
+      <c r="F60" s="64" t="inlineStr">
         <is>
           <t>Surat pernyataan kesanggupan harga dan masa berlaku penawaran.</t>
         </is>
       </c>
-      <c r="G60" s="16" t="inlineStr">
+      <c r="G60" s="64" t="inlineStr">
         <is>
           <t>F13.pdf (Path: AKIP PKTJ 2025\Indikator F\F13.pdf)</t>
         </is>
       </c>
-      <c r="H60" s="52" t="inlineStr">
+      <c r="H60" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I60" s="52" t="n"/>
-      <c r="J60" s="52" t="n"/>
+      <c r="I60" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J60" s="70" t="inlineStr"/>
       <c r="K60" s="52" t="n"/>
       <c r="L60" s="52" t="n"/>
       <c r="M60" s="52" t="n"/>
@@ -3947,42 +4340,46 @@
       <c r="AB60" s="52" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="52" t="n"/>
-      <c r="B61" s="11" t="n">
+      <c r="A61" s="64" t="n"/>
+      <c r="B61" s="65" t="n">
         <v>13</v>
       </c>
-      <c r="C61" s="43" t="inlineStr">
+      <c r="C61" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Surat Penawaran Penyedia ?</t>
         </is>
       </c>
-      <c r="D61" s="16" t="inlineStr">
+      <c r="D61" s="64" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="E61" s="37" t="inlineStr">
+      <c r="E61" s="85" t="inlineStr">
         <is>
           <t>Surat Pernyataan Direktur: Paket Pekerjaan Tidak Mensyaratkan Lisensi HAKI</t>
         </is>
       </c>
-      <c r="F61" s="16" t="inlineStr">
+      <c r="F61" s="64" t="inlineStr">
         <is>
           <t>Surat pernyataan resmi bertandatangan Direktur PKTJ sesuai panduan AKIP Slide 63.</t>
         </is>
       </c>
-      <c r="G61" s="16" t="inlineStr">
+      <c r="G61" s="64" t="inlineStr">
         <is>
           <t>Pernyataan Direktur untuk AKIP.pdf (Path: AKIP PKTJ 2025\Indikator F\Surat Pernyataan Direktur\Pernyataan Direktur untuk AKIP.pdf)</t>
         </is>
       </c>
-      <c r="H61" s="52" t="inlineStr">
+      <c r="H61" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I61" s="52" t="n"/>
-      <c r="J61" s="52" t="n"/>
+      <c r="I61" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J61" s="70" t="inlineStr"/>
       <c r="K61" s="52" t="n"/>
       <c r="L61" s="52" t="n"/>
       <c r="M61" s="52" t="n"/>
@@ -4003,42 +4400,46 @@
       <c r="AB61" s="52" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="52" t="n"/>
-      <c r="B62" s="11" t="n">
+      <c r="A62" s="64" t="n"/>
+      <c r="B62" s="65" t="n">
         <v>14</v>
       </c>
-      <c r="C62" s="43" t="inlineStr">
+      <c r="C62" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Sertifikat atau Lisensi yang masih berlaku dari Direktorat Jenderal Kekayaan Intelektual Kementerian Hukum dan Hak Asasi Manusia ?</t>
         </is>
       </c>
-      <c r="D62" s="16" t="inlineStr">
+      <c r="D62" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E62" s="16" t="inlineStr">
+      <c r="E62" s="64" t="inlineStr">
         <is>
           <t>Berita Acara Pemberian Penjelasan Pekerjaan (Aanwijzing)</t>
         </is>
       </c>
-      <c r="F62" s="16" t="inlineStr">
+      <c r="F62" s="64" t="inlineStr">
         <is>
           <t>Notulensi tanya jawab teknis pelaksanaan pengadaan.</t>
         </is>
       </c>
-      <c r="G62" s="37" t="inlineStr">
+      <c r="G62" s="85" t="inlineStr">
         <is>
           <t>F15.pdf (Path: AKIP PKTJ 2025\Indikator F\F15.pdf)</t>
         </is>
       </c>
-      <c r="H62" s="52" t="inlineStr">
+      <c r="H62" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I62" s="52" t="n"/>
-      <c r="J62" s="52" t="n"/>
+      <c r="I62" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J62" s="70" t="inlineStr"/>
       <c r="K62" s="52" t="n"/>
       <c r="L62" s="52" t="n"/>
       <c r="M62" s="52" t="n"/>
@@ -4059,42 +4460,46 @@
       <c r="AB62" s="52" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="52" t="n"/>
-      <c r="B63" s="11" t="n">
+      <c r="A63" s="64" t="n"/>
+      <c r="B63" s="65" t="n">
         <v>15</v>
       </c>
-      <c r="C63" s="43" t="inlineStr">
+      <c r="C63" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Berita Acara Pemberian Penjelasan ?</t>
         </is>
       </c>
-      <c r="D63" s="16" t="inlineStr">
+      <c r="D63" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E63" s="37" t="inlineStr">
+      <c r="E63" s="85" t="inlineStr">
         <is>
           <t>Berita Acara Hasil Klarifikasi dan Negosiasi Teknis &amp; Biaya</t>
         </is>
       </c>
-      <c r="F63" s="16" t="inlineStr">
+      <c r="F63" s="64" t="inlineStr">
         <is>
           <t>Kesepakatan akhir negosiasi harga penawaran pengadaan.</t>
         </is>
       </c>
-      <c r="G63" s="16" t="inlineStr">
+      <c r="G63" s="64" t="inlineStr">
         <is>
           <t>F16.pdf (Path: AKIP PKTJ 2025\Indikator F\F16.pdf)</t>
         </is>
       </c>
-      <c r="H63" s="52" t="inlineStr">
+      <c r="H63" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I63" s="52" t="n"/>
-      <c r="J63" s="52" t="n"/>
+      <c r="I63" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J63" s="70" t="inlineStr"/>
       <c r="K63" s="52" t="n"/>
       <c r="L63" s="52" t="n"/>
       <c r="M63" s="52" t="n"/>
@@ -4115,42 +4520,46 @@
       <c r="AB63" s="52" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="52" t="n"/>
-      <c r="B64" s="11" t="n">
+      <c r="A64" s="64" t="n"/>
+      <c r="B64" s="65" t="n">
         <v>16</v>
       </c>
-      <c r="C64" s="43" t="inlineStr">
+      <c r="C64" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Berita Acara Pengumuman Negosiasi ?</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="D64" s="64" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="E64" s="37" t="inlineStr">
+      <c r="E64" s="85" t="inlineStr">
         <is>
           <t>Surat Pernyataan Direktur: Masa Sanggah Selesai Tanpa Sanggahan (Nihil)</t>
         </is>
       </c>
-      <c r="F64" s="16" t="inlineStr">
+      <c r="F64" s="64" t="inlineStr">
         <is>
           <t>Surat pernyataan resmi bertandatangan Direktur PKTJ sesuai panduan AKIP Slide 63.</t>
         </is>
       </c>
-      <c r="G64" s="16" t="inlineStr">
+      <c r="G64" s="64" t="inlineStr">
         <is>
           <t>Pernyataan Direktur untuk AKIP.pdf (Path: AKIP PKTJ 2025\Indikator F\Surat Pernyataan Direktur\Pernyataan Direktur untuk AKIP.pdf)</t>
         </is>
       </c>
-      <c r="H64" s="52" t="inlineStr">
+      <c r="H64" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I64" s="52" t="n"/>
-      <c r="J64" s="52" t="n"/>
+      <c r="I64" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J64" s="70" t="inlineStr"/>
       <c r="K64" s="52" t="n"/>
       <c r="L64" s="52" t="n"/>
       <c r="M64" s="52" t="n"/>
@@ -4171,42 +4580,46 @@
       <c r="AB64" s="52" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="52" t="n"/>
-      <c r="B65" s="11" t="n">
+      <c r="A65" s="64" t="n"/>
+      <c r="B65" s="65" t="n">
         <v>17</v>
       </c>
-      <c r="C65" s="43" t="inlineStr">
+      <c r="C65" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Berita Acara Sanggah dan Sanggah Banding ?</t>
         </is>
       </c>
-      <c r="D65" s="16" t="inlineStr">
+      <c r="D65" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E65" s="16" t="inlineStr">
+      <c r="E65" s="64" t="inlineStr">
         <is>
           <t>Berita Acara Penetapan dan Pengumuman Pemenang Penyedia Barang/Jasa</t>
         </is>
       </c>
-      <c r="F65" s="16" t="inlineStr">
+      <c r="F65" s="64" t="inlineStr">
         <is>
           <t>Surat ketetapan penunjukan calon pemenang hasil evaluasi Pokja.</t>
         </is>
       </c>
-      <c r="G65" s="37" t="inlineStr">
+      <c r="G65" s="85" t="inlineStr">
         <is>
           <t>F18.pdf (Path: AKIP PKTJ 2025\Indikator F\F18.pdf)</t>
         </is>
       </c>
-      <c r="H65" s="52" t="inlineStr">
+      <c r="H65" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I65" s="52" t="n"/>
-      <c r="J65" s="52" t="n"/>
+      <c r="I65" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J65" s="70" t="inlineStr"/>
       <c r="K65" s="52" t="n"/>
       <c r="L65" s="52" t="n"/>
       <c r="M65" s="52" t="n"/>
@@ -4227,42 +4640,46 @@
       <c r="AB65" s="52" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="52" t="n"/>
-      <c r="B66" s="11" t="n">
+      <c r="A66" s="64" t="n"/>
+      <c r="B66" s="65" t="n">
         <v>18</v>
       </c>
-      <c r="C66" s="43" t="inlineStr">
+      <c r="C66" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Berita Acara Penetapan atau Pengumuman Penyedia ?</t>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="D66" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E66" s="37" t="inlineStr">
+      <c r="E66" s="85" t="inlineStr">
         <is>
           <t>Laporan Hasil Pemilihan Penyedia Barang dan Jasa oleh Pokja Pemilihan</t>
         </is>
       </c>
-      <c r="F66" s="16" t="inlineStr">
+      <c r="F66" s="64" t="inlineStr">
         <is>
           <t>Laporan rekapitulasi evaluasi administrasi, teknis, dan harga.</t>
         </is>
       </c>
-      <c r="G66" s="16" t="inlineStr">
+      <c r="G66" s="64" t="inlineStr">
         <is>
           <t>F19.pdf (Path: AKIP PKTJ 2025\Indikator F\F19.pdf)</t>
         </is>
       </c>
-      <c r="H66" s="52" t="inlineStr">
+      <c r="H66" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I66" s="52" t="n"/>
-      <c r="J66" s="52" t="n"/>
+      <c r="I66" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J66" s="70" t="inlineStr"/>
       <c r="K66" s="52" t="n"/>
       <c r="L66" s="52" t="n"/>
       <c r="M66" s="52" t="n"/>
@@ -4283,42 +4700,46 @@
       <c r="AB66" s="52" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="52" t="n"/>
-      <c r="B67" s="11" t="n">
+      <c r="A67" s="64" t="n"/>
+      <c r="B67" s="65" t="n">
         <v>19</v>
       </c>
-      <c r="C67" s="43" t="inlineStr">
+      <c r="C67" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Laporan Hasil Pemilihan Penyedia ?</t>
         </is>
       </c>
-      <c r="D67" s="16" t="inlineStr">
+      <c r="D67" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E67" s="37" t="inlineStr">
+      <c r="E67" s="85" t="inlineStr">
         <is>
           <t>Surat Penunjukan Penyedia Barang/Jasa (SPPBJ) dari PPK PKTJ</t>
         </is>
       </c>
-      <c r="F67" s="16" t="inlineStr">
+      <c r="F67" s="64" t="inlineStr">
         <is>
           <t>Surat resmi penunjukan penyedia sebelum penandatanganan kontrak.</t>
         </is>
       </c>
-      <c r="G67" s="16" t="inlineStr">
+      <c r="G67" s="64" t="inlineStr">
         <is>
           <t>F20.pdf (Path: AKIP PKTJ 2025\Indikator F\F20.pdf)</t>
         </is>
       </c>
-      <c r="H67" s="52" t="inlineStr">
+      <c r="H67" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I67" s="52" t="n"/>
-      <c r="J67" s="52" t="n"/>
+      <c r="I67" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J67" s="70" t="inlineStr"/>
       <c r="K67" s="52" t="n"/>
       <c r="L67" s="52" t="n"/>
       <c r="M67" s="52" t="n"/>
@@ -4339,42 +4760,46 @@
       <c r="AB67" s="52" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="52" t="n"/>
-      <c r="B68" s="11" t="n">
+      <c r="A68" s="64" t="n"/>
+      <c r="B68" s="65" t="n">
         <v>20</v>
       </c>
-      <c r="C68" s="43" t="inlineStr">
+      <c r="C68" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Surat Penunjukan Penyedia Barang/Jasa (SPPBJ) ?</t>
         </is>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D68" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E68" s="37" t="inlineStr">
+      <c r="E68" s="85" t="inlineStr">
         <is>
           <t>Dokumen Surat Perjanjian Kemitraan Kerja Sama Operasional</t>
         </is>
       </c>
-      <c r="F68" s="16" t="inlineStr">
+      <c r="F68" s="64" t="inlineStr">
         <is>
           <t>Naskah perjanjian kemitraan penyedia.</t>
         </is>
       </c>
-      <c r="G68" s="16" t="inlineStr">
+      <c r="G68" s="64" t="inlineStr">
         <is>
           <t>F21.pdf (Path: AKIP PKTJ 2025\Indikator F\F21.pdf)</t>
         </is>
       </c>
-      <c r="H68" s="52" t="inlineStr">
+      <c r="H68" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I68" s="52" t="n"/>
-      <c r="J68" s="52" t="n"/>
+      <c r="I68" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J68" s="70" t="inlineStr"/>
       <c r="K68" s="52" t="n"/>
       <c r="L68" s="52" t="n"/>
       <c r="M68" s="52" t="n"/>
@@ -4395,42 +4820,46 @@
       <c r="AB68" s="52" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="52" t="n"/>
-      <c r="B69" s="11" t="n">
+      <c r="A69" s="64" t="n"/>
+      <c r="B69" s="65" t="n">
         <v>21</v>
       </c>
-      <c r="C69" s="43" t="inlineStr">
+      <c r="C69" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Surat Perjanjian Kemitraan ?</t>
         </is>
       </c>
-      <c r="D69" s="16" t="inlineStr">
+      <c r="D69" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E69" s="37" t="inlineStr">
+      <c r="E69" s="85" t="inlineStr">
         <is>
           <t>Surat Keputusan Penetapan Tim Pelaksana Swakelola Pekerjaan</t>
         </is>
       </c>
-      <c r="F69" s="16" t="inlineStr">
+      <c r="F69" s="64" t="inlineStr">
         <is>
           <t>SK pembentukan dan penugasan tim perencana dan pengawas swakelola.</t>
         </is>
       </c>
-      <c r="G69" s="16" t="inlineStr">
+      <c r="G69" s="64" t="inlineStr">
         <is>
           <t>F22.pdf (Path: AKIP PKTJ 2025\Indikator F\F22.pdf)</t>
         </is>
       </c>
-      <c r="H69" s="52" t="inlineStr">
+      <c r="H69" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I69" s="52" t="n"/>
-      <c r="J69" s="52" t="n"/>
+      <c r="I69" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J69" s="70" t="inlineStr"/>
       <c r="K69" s="52" t="n"/>
       <c r="L69" s="52" t="n"/>
       <c r="M69" s="52" t="n"/>
@@ -4451,42 +4880,46 @@
       <c r="AB69" s="52" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="52" t="n"/>
-      <c r="B70" s="11" t="n">
+      <c r="A70" s="64" t="n"/>
+      <c r="B70" s="65" t="n">
         <v>22</v>
       </c>
-      <c r="C70" s="43" t="inlineStr">
+      <c r="C70" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Surat Penugasan atau Surat Pembentukan Tim Swakelola ?</t>
         </is>
       </c>
-      <c r="D70" s="16" t="inlineStr">
+      <c r="D70" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E70" s="37" t="inlineStr">
+      <c r="E70" s="85" t="inlineStr">
         <is>
           <t>Nota Kesepahaman (Memorandum of Understanding) Pengadaan</t>
         </is>
       </c>
-      <c r="F70" s="16" t="inlineStr">
+      <c r="F70" s="64" t="inlineStr">
         <is>
           <t>Naskah kesepahaman pelaksanaan kegiatan bersama.</t>
         </is>
       </c>
-      <c r="G70" s="16" t="inlineStr">
+      <c r="G70" s="64" t="inlineStr">
         <is>
           <t>F23.pdf (Path: AKIP PKTJ 2025\Indikator F\F23.pdf)</t>
         </is>
       </c>
-      <c r="H70" s="52" t="inlineStr">
+      <c r="H70" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I70" s="52" t="n"/>
-      <c r="J70" s="52" t="n"/>
+      <c r="I70" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J70" s="70" t="inlineStr"/>
       <c r="K70" s="52" t="n"/>
       <c r="L70" s="52" t="n"/>
       <c r="M70" s="52" t="n"/>
@@ -4507,42 +4940,46 @@
       <c r="AB70" s="52" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="52" t="n"/>
-      <c r="B71" s="11" t="n">
+      <c r="A71" s="64" t="n"/>
+      <c r="B71" s="65" t="n">
         <v>23</v>
       </c>
-      <c r="C71" s="43" t="inlineStr">
+      <c r="C71" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Nota Kesepahaman atau Memorandum of Understanding ?</t>
         </is>
       </c>
-      <c r="D71" s="16" t="inlineStr">
+      <c r="D71" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E71" s="21" t="inlineStr">
+      <c r="E71" s="71" t="inlineStr">
         <is>
           <t>Dokumen Surat Perjanjian Kontrak Pengadaan Ditandatangani (Tersensor)</t>
         </is>
       </c>
-      <c r="F71" s="16" t="inlineStr">
+      <c r="F71" s="64" t="inlineStr">
         <is>
           <t>Salinan resmi kontrak kerja yang telah dilakukan penghitaman/pemburaman pada data dikecualikan.</t>
         </is>
       </c>
-      <c r="G71" s="16" t="inlineStr">
+      <c r="G71" s="64" t="inlineStr">
         <is>
           <t>F24.pdf (Path: AKIP PKTJ 2025\Indikator F\F24.pdf)</t>
         </is>
       </c>
-      <c r="H71" s="52" t="inlineStr">
+      <c r="H71" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I71" s="52" t="n"/>
-      <c r="J71" s="52" t="n"/>
+      <c r="I71" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J71" s="70" t="inlineStr"/>
       <c r="K71" s="52" t="n"/>
       <c r="L71" s="52" t="n"/>
       <c r="M71" s="52" t="n"/>
@@ -4563,42 +5000,46 @@
       <c r="AB71" s="52" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="52" t="n"/>
-      <c r="B72" s="11" t="n">
+      <c r="A72" s="64" t="n"/>
+      <c r="B72" s="65" t="n">
         <v>24</v>
       </c>
-      <c r="C72" s="45" t="inlineStr">
+      <c r="C72" s="91" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Dokumen Kontrak yang telah ditandatangani beserta Perubahan Kontrak yang tidak mengandung informasi yang dikecualikan ?</t>
         </is>
       </c>
-      <c r="D72" s="16" t="inlineStr">
+      <c r="D72" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E72" s="46" t="inlineStr">
+      <c r="E72" s="93" t="inlineStr">
         <is>
           <t>Ringkasan Eksekutif Kontrak Pengadaan Barang dan Jasa PKTJ</t>
         </is>
       </c>
-      <c r="F72" s="16" t="inlineStr">
+      <c r="F72" s="64" t="inlineStr">
         <is>
           <t>Resume para pihak, nomor kontrak, nilai kontrak, waktu pelaksanaan, dan sumber dana.</t>
         </is>
       </c>
-      <c r="G72" s="16" t="inlineStr">
+      <c r="G72" s="64" t="inlineStr">
         <is>
           <t>F25.pdf (Path: AKIP PKTJ 2025\Indikator F\F25.pdf)</t>
         </is>
       </c>
-      <c r="H72" s="52" t="inlineStr">
+      <c r="H72" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I72" s="52" t="n"/>
-      <c r="J72" s="52" t="n"/>
+      <c r="I72" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J72" s="70" t="inlineStr"/>
       <c r="K72" s="52" t="n"/>
       <c r="L72" s="52" t="n"/>
       <c r="M72" s="52" t="n"/>
@@ -4619,42 +5060,46 @@
       <c r="AB72" s="52" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="52" t="n"/>
-      <c r="B73" s="11" t="n">
+      <c r="A73" s="64" t="n"/>
+      <c r="B73" s="65" t="n">
         <v>25</v>
       </c>
-      <c r="C73" s="47" t="inlineStr">
+      <c r="C73" s="94" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Ringkasan Kontrak yang sekurang-kurangnya mencantumkan informasi mengenai para pihak yang bertandatangan, nama direktur dan pemilik usaha, alamat penyedia, NPWP, nilai kontrak, rincian pekerjaan, spesifikasi pekerjaan, lokasi pekerjaan, waktu pekerjaan, sumber dana, jenis kontrak, serta ringkasan perubahan kontrak ?</t>
         </is>
       </c>
-      <c r="D73" s="16" t="inlineStr">
+      <c r="D73" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E73" s="21" t="inlineStr">
+      <c r="E73" s="71" t="inlineStr">
         <is>
           <t>Surat Perintah Mulai Kerja (SPMK) dari Pejabat Pembuat Komitmen</t>
         </is>
       </c>
-      <c r="F73" s="16" t="inlineStr">
+      <c r="F73" s="64" t="inlineStr">
         <is>
           <t>Surat perintah resmi kepada penyedia untuk memulai pelaksanaan pekerjaan.</t>
         </is>
       </c>
-      <c r="G73" s="16" t="inlineStr">
+      <c r="G73" s="64" t="inlineStr">
         <is>
           <t>F26.pdf (Path: AKIP PKTJ 2025\Indikator F\F26.pdf)</t>
         </is>
       </c>
-      <c r="H73" s="52" t="inlineStr">
+      <c r="H73" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I73" s="52" t="n"/>
-      <c r="J73" s="52" t="n"/>
+      <c r="I73" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J73" s="70" t="inlineStr"/>
       <c r="K73" s="52" t="n"/>
       <c r="L73" s="52" t="n"/>
       <c r="M73" s="52" t="n"/>
@@ -4675,42 +5120,46 @@
       <c r="AB73" s="52" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="52" t="n"/>
-      <c r="B74" s="11" t="n">
+      <c r="A74" s="64" t="n"/>
+      <c r="B74" s="65" t="n">
         <v>26</v>
       </c>
-      <c r="C74" s="43" t="inlineStr">
+      <c r="C74" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Surat Perintah Mulai Kerja ?</t>
         </is>
       </c>
-      <c r="D74" s="16" t="inlineStr">
+      <c r="D74" s="64" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="E74" s="21" t="inlineStr">
+      <c r="E74" s="71" t="inlineStr">
         <is>
           <t>Surat Pernyataan Direktur: Paket Pekerjaan Tidak Mensyaratkan Jaminan Pelaksanaan</t>
         </is>
       </c>
-      <c r="F74" s="16" t="inlineStr">
+      <c r="F74" s="64" t="inlineStr">
         <is>
           <t>Surat pernyataan resmi bertandatangan Direktur PKTJ sesuai panduan AKIP Slide 63.</t>
         </is>
       </c>
-      <c r="G74" s="16" t="inlineStr">
+      <c r="G74" s="64" t="inlineStr">
         <is>
           <t>Pernyataan Direktur untuk AKIP.pdf (Path: AKIP PKTJ 2025\Indikator F\Surat Pernyataan Direktur\Pernyataan Direktur untuk AKIP.pdf)</t>
         </is>
       </c>
-      <c r="H74" s="52" t="inlineStr">
+      <c r="H74" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I74" s="52" t="n"/>
-      <c r="J74" s="52" t="n"/>
+      <c r="I74" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J74" s="70" t="inlineStr"/>
       <c r="K74" s="52" t="n"/>
       <c r="L74" s="52" t="n"/>
       <c r="M74" s="52" t="n"/>
@@ -4731,42 +5180,46 @@
       <c r="AB74" s="52" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="52" t="n"/>
-      <c r="B75" s="11" t="n">
+      <c r="A75" s="64" t="n"/>
+      <c r="B75" s="65" t="n">
         <v>27</v>
       </c>
-      <c r="C75" s="43" t="inlineStr">
+      <c r="C75" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Surat Jaminan Pelaksanaan ?</t>
         </is>
       </c>
-      <c r="D75" s="16" t="inlineStr">
+      <c r="D75" s="64" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="E75" s="16" t="inlineStr">
+      <c r="E75" s="64" t="inlineStr">
         <is>
           <t>Surat Pernyataan Direktur: Pembayaran Dilakukan Tanpa Uang Muka (Termin)</t>
         </is>
       </c>
-      <c r="F75" s="16" t="inlineStr">
+      <c r="F75" s="64" t="inlineStr">
         <is>
           <t>Surat pernyataan resmi bertandatangan Direktur PKTJ sesuai panduan AKIP Slide 63.</t>
         </is>
       </c>
-      <c r="G75" s="37" t="inlineStr">
+      <c r="G75" s="85" t="inlineStr">
         <is>
           <t>Pernyataan Direktur untuk AKIP.pdf (Path: AKIP PKTJ 2025\Indikator F\Surat Pernyataan Direktur\Pernyataan Direktur untuk AKIP.pdf)</t>
         </is>
       </c>
-      <c r="H75" s="52" t="inlineStr">
+      <c r="H75" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I75" s="52" t="n"/>
-      <c r="J75" s="52" t="n"/>
+      <c r="I75" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J75" s="70" t="inlineStr"/>
       <c r="K75" s="52" t="n"/>
       <c r="L75" s="52" t="n"/>
       <c r="M75" s="52" t="n"/>
@@ -4787,42 +5240,46 @@
       <c r="AB75" s="52" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="52" t="n"/>
-      <c r="B76" s="11" t="n">
+      <c r="A76" s="64" t="n"/>
+      <c r="B76" s="65" t="n">
         <v>28</v>
       </c>
-      <c r="C76" s="43" t="inlineStr">
+      <c r="C76" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Surat Jaminan Uang Muka ?</t>
         </is>
       </c>
-      <c r="D76" s="16" t="inlineStr">
+      <c r="D76" s="64" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="E76" s="16" t="inlineStr">
+      <c r="E76" s="64" t="inlineStr">
         <is>
           <t>Surat Pernyataan Direktur: Pemeliharaan Menggunakan Sistem Retensi Pembayaran</t>
         </is>
       </c>
-      <c r="F76" s="16" t="inlineStr">
+      <c r="F76" s="64" t="inlineStr">
         <is>
           <t>Surat pernyataan resmi bertandatangan Direktur PKTJ sesuai panduan AKIP Slide 63.</t>
         </is>
       </c>
-      <c r="G76" s="37" t="inlineStr">
+      <c r="G76" s="85" t="inlineStr">
         <is>
           <t>Pernyataan Direktur untuk AKIP.pdf (Path: AKIP PKTJ 2025\Indikator F\Surat Pernyataan Direktur\Pernyataan Direktur untuk AKIP.pdf)</t>
         </is>
       </c>
-      <c r="H76" s="52" t="inlineStr">
+      <c r="H76" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I76" s="52" t="n"/>
-      <c r="J76" s="52" t="n"/>
+      <c r="I76" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J76" s="70" t="inlineStr"/>
       <c r="K76" s="52" t="n"/>
       <c r="L76" s="52" t="n"/>
       <c r="M76" s="52" t="n"/>
@@ -4843,42 +5300,46 @@
       <c r="AB76" s="52" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="52" t="n"/>
-      <c r="B77" s="11" t="n">
+      <c r="A77" s="64" t="n"/>
+      <c r="B77" s="65" t="n">
         <v>29</v>
       </c>
-      <c r="C77" s="43" t="inlineStr">
+      <c r="C77" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Surat Jaminan Pemeliharaan ?</t>
         </is>
       </c>
-      <c r="D77" s="16" t="inlineStr">
+      <c r="D77" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E77" s="16" t="inlineStr">
+      <c r="E77" s="64" t="inlineStr">
         <is>
           <t>Surat Tagihan Pembayaran dan Kuitansi dari Penyedia Barang/Jasa</t>
         </is>
       </c>
-      <c r="F77" s="16" t="inlineStr">
+      <c r="F77" s="64" t="inlineStr">
         <is>
           <t>Kuitansi dan invoice permohonan pembayaran atas kemajuan pekerjaan.</t>
         </is>
       </c>
-      <c r="G77" s="37" t="inlineStr">
+      <c r="G77" s="85" t="inlineStr">
         <is>
           <t>F30.pdf (Path: AKIP PKTJ 2025\Indikator F\F30.pdf)</t>
         </is>
       </c>
-      <c r="H77" s="52" t="inlineStr">
+      <c r="H77" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I77" s="52" t="n"/>
-      <c r="J77" s="52" t="n"/>
+      <c r="I77" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J77" s="70" t="inlineStr"/>
       <c r="K77" s="52" t="n"/>
       <c r="L77" s="52" t="n"/>
       <c r="M77" s="52" t="n"/>
@@ -4899,42 +5360,46 @@
       <c r="AB77" s="52" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="52" t="n"/>
-      <c r="B78" s="11" t="n">
+      <c r="A78" s="64" t="n"/>
+      <c r="B78" s="65" t="n">
         <v>30</v>
       </c>
-      <c r="C78" s="43" t="inlineStr">
+      <c r="C78" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Surat Tagihan ?</t>
         </is>
       </c>
-      <c r="D78" s="16" t="inlineStr">
+      <c r="D78" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E78" s="21" t="inlineStr">
+      <c r="E78" s="71" t="inlineStr">
         <is>
           <t>Surat Pesanan E-Purchasing Melalui Katalog Elektronik LKPP</t>
         </is>
       </c>
-      <c r="F78" s="16" t="inlineStr">
+      <c r="F78" s="64" t="inlineStr">
         <is>
           <t>Bukti pesanan transaksi elektronik pengadaan barang/jasa.</t>
         </is>
       </c>
-      <c r="G78" s="16" t="inlineStr">
+      <c r="G78" s="64" t="inlineStr">
         <is>
           <t>F31.pdf (Path: AKIP PKTJ 2025\Indikator F\F31.pdf)</t>
         </is>
       </c>
-      <c r="H78" s="52" t="inlineStr">
+      <c r="H78" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I78" s="52" t="n"/>
-      <c r="J78" s="52" t="n"/>
+      <c r="I78" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J78" s="70" t="inlineStr"/>
       <c r="K78" s="52" t="n"/>
       <c r="L78" s="52" t="n"/>
       <c r="M78" s="52" t="n"/>
@@ -4955,42 +5420,46 @@
       <c r="AB78" s="52" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="52" t="n"/>
-      <c r="B79" s="11" t="n">
+      <c r="A79" s="64" t="n"/>
+      <c r="B79" s="65" t="n">
         <v>31</v>
       </c>
-      <c r="C79" s="43" t="inlineStr">
+      <c r="C79" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Surat Pesanan E-purchasing ?</t>
         </is>
       </c>
-      <c r="D79" s="16" t="inlineStr">
+      <c r="D79" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E79" s="21" t="inlineStr">
+      <c r="E79" s="71" t="inlineStr">
         <is>
           <t>Surat Perintah Membayar (SPM) Pejabat Penandatangan SPM PKTJ</t>
         </is>
       </c>
-      <c r="F79" s="16" t="inlineStr">
+      <c r="F79" s="64" t="inlineStr">
         <is>
           <t>Dokumen perintah pembayaran dari PPSPM kepada Kantor Pelayanan Perbendaharaan Negara.</t>
         </is>
       </c>
-      <c r="G79" s="16" t="inlineStr">
+      <c r="G79" s="64" t="inlineStr">
         <is>
           <t>F32.pdf (Path: AKIP PKTJ 2025\Indikator F\F32.pdf)</t>
         </is>
       </c>
-      <c r="H79" s="52" t="inlineStr">
+      <c r="H79" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I79" s="52" t="n"/>
-      <c r="J79" s="52" t="n"/>
+      <c r="I79" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J79" s="70" t="inlineStr"/>
       <c r="K79" s="52" t="n"/>
       <c r="L79" s="52" t="n"/>
       <c r="M79" s="52" t="n"/>
@@ -5011,42 +5480,46 @@
       <c r="AB79" s="52" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="52" t="n"/>
-      <c r="B80" s="11" t="n">
+      <c r="A80" s="64" t="n"/>
+      <c r="B80" s="65" t="n">
         <v>32</v>
       </c>
-      <c r="C80" s="43" t="inlineStr">
+      <c r="C80" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Surat Perintah Membayar ?</t>
         </is>
       </c>
-      <c r="D80" s="16" t="inlineStr">
+      <c r="D80" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E80" s="21" t="inlineStr">
+      <c r="E80" s="71" t="inlineStr">
         <is>
           <t>Surat Perintah Pencairan Dana (SP2D) KPPN Tegal</t>
         </is>
       </c>
-      <c r="F80" s="16" t="inlineStr">
+      <c r="F80" s="64" t="inlineStr">
         <is>
           <t>Bukti transfer pencairan dana anggaran dari kas negara ke rekening penyedia.</t>
         </is>
       </c>
-      <c r="G80" s="16" t="inlineStr">
+      <c r="G80" s="64" t="inlineStr">
         <is>
           <t>F33.pdf (Path: AKIP PKTJ 2025\Indikator F\F33.pdf)</t>
         </is>
       </c>
-      <c r="H80" s="52" t="inlineStr">
+      <c r="H80" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I80" s="52" t="n"/>
-      <c r="J80" s="52" t="n"/>
+      <c r="I80" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J80" s="70" t="inlineStr"/>
       <c r="K80" s="52" t="n"/>
       <c r="L80" s="52" t="n"/>
       <c r="M80" s="52" t="n"/>
@@ -5067,42 +5540,46 @@
       <c r="AB80" s="52" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="52" t="n"/>
-      <c r="B81" s="11" t="n">
+      <c r="A81" s="64" t="n"/>
+      <c r="B81" s="65" t="n">
         <v>33</v>
       </c>
-      <c r="C81" s="43" t="inlineStr">
+      <c r="C81" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Surat Perintah Membayar ?</t>
         </is>
       </c>
-      <c r="D81" s="16" t="inlineStr">
+      <c r="D81" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E81" s="21" t="inlineStr">
+      <c r="E81" s="71" t="inlineStr">
         <is>
           <t>Laporan Kemajuan dan Pelaksanaan Pekerjaan Berkala</t>
         </is>
       </c>
-      <c r="F81" s="16" t="inlineStr">
+      <c r="F81" s="64" t="inlineStr">
         <is>
           <t>Laporan mingguan dan bulanan progres fisik di lapangan oleh konsultan pengawas.</t>
         </is>
       </c>
-      <c r="G81" s="16" t="inlineStr">
+      <c r="G81" s="64" t="inlineStr">
         <is>
           <t>F34.pdf (Path: AKIP PKTJ 2025\Indikator F\F34.pdf)</t>
         </is>
       </c>
-      <c r="H81" s="52" t="inlineStr">
+      <c r="H81" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I81" s="52" t="n"/>
-      <c r="J81" s="52" t="n"/>
+      <c r="I81" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J81" s="70" t="inlineStr"/>
       <c r="K81" s="52" t="n"/>
       <c r="L81" s="52" t="n"/>
       <c r="M81" s="52" t="n"/>
@@ -5123,42 +5600,46 @@
       <c r="AB81" s="52" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="52" t="n"/>
-      <c r="B82" s="11" t="n">
+      <c r="A82" s="64" t="n"/>
+      <c r="B82" s="65" t="n">
         <v>34</v>
       </c>
-      <c r="C82" s="43" t="inlineStr">
+      <c r="C82" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Laporan Pelaksanaan Pekerjaan ?</t>
         </is>
       </c>
-      <c r="D82" s="16" t="inlineStr">
+      <c r="D82" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E82" s="21" t="inlineStr">
+      <c r="E82" s="71" t="inlineStr">
         <is>
           <t>Laporan Akhir Penyelesaian Pekerjaan (Progres 100%)</t>
         </is>
       </c>
-      <c r="F82" s="16" t="inlineStr">
+      <c r="F82" s="64" t="inlineStr">
         <is>
           <t>Laporan final kelengkapan dan selesainya seluruh volume pekerjaan.</t>
         </is>
       </c>
-      <c r="G82" s="16" t="inlineStr">
+      <c r="G82" s="64" t="inlineStr">
         <is>
           <t>F35.pdf (Path: AKIP PKTJ 2025\Indikator F\F35.pdf)</t>
         </is>
       </c>
-      <c r="H82" s="52" t="inlineStr">
+      <c r="H82" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I82" s="52" t="n"/>
-      <c r="J82" s="52" t="n"/>
+      <c r="I82" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J82" s="70" t="inlineStr"/>
       <c r="K82" s="52" t="n"/>
       <c r="L82" s="52" t="n"/>
       <c r="M82" s="52" t="n"/>
@@ -5179,42 +5660,46 @@
       <c r="AB82" s="52" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="52" t="n"/>
-      <c r="B83" s="11" t="n">
+      <c r="A83" s="64" t="n"/>
+      <c r="B83" s="65" t="n">
         <v>35</v>
       </c>
-      <c r="C83" s="43" t="inlineStr">
+      <c r="C83" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Laporan Penyelesaian Pekerjaan ?</t>
         </is>
       </c>
-      <c r="D83" s="16" t="inlineStr">
+      <c r="D83" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E83" s="21" t="inlineStr">
+      <c r="E83" s="71" t="inlineStr">
         <is>
           <t>Berita Acara Pemeriksaan Hasil Pekerjaan (BAPHP) oleh Tim Teknis</t>
         </is>
       </c>
-      <c r="F83" s="16" t="inlineStr">
+      <c r="F83" s="64" t="inlineStr">
         <is>
           <t>Berita acara hasil uji sampling dan inspeksi mutu pekerjaan di lapangan.</t>
         </is>
       </c>
-      <c r="G83" s="16" t="inlineStr">
+      <c r="G83" s="64" t="inlineStr">
         <is>
           <t>F36.pdf (Path: AKIP PKTJ 2025\Indikator F\F36.pdf)</t>
         </is>
       </c>
-      <c r="H83" s="52" t="inlineStr">
+      <c r="H83" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I83" s="52" t="n"/>
-      <c r="J83" s="52" t="n"/>
+      <c r="I83" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J83" s="70" t="inlineStr"/>
       <c r="K83" s="52" t="n"/>
       <c r="L83" s="52" t="n"/>
       <c r="M83" s="52" t="n"/>
@@ -5235,42 +5720,46 @@
       <c r="AB83" s="52" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="52" t="n"/>
-      <c r="B84" s="11" t="n">
+      <c r="A84" s="64" t="n"/>
+      <c r="B84" s="65" t="n">
         <v>36</v>
       </c>
-      <c r="C84" s="43" t="inlineStr">
+      <c r="C84" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Berita Acara Pemeriksaan Hasil Pekerjaan ?</t>
         </is>
       </c>
-      <c r="D84" s="16" t="inlineStr">
+      <c r="D84" s="64" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="E84" s="21" t="inlineStr">
+      <c r="E84" s="71" t="inlineStr">
         <is>
           <t>Surat Pernyataan Direktur: Pengadaan Barang Habis Pakai / Non-PHO</t>
         </is>
       </c>
-      <c r="F84" s="16" t="inlineStr">
+      <c r="F84" s="64" t="inlineStr">
         <is>
           <t>Surat pernyataan resmi bertandatangan Direktur PKTJ sesuai panduan AKIP Slide 63.</t>
         </is>
       </c>
-      <c r="G84" s="16" t="inlineStr">
+      <c r="G84" s="64" t="inlineStr">
         <is>
           <t>Pernyataan Direktur untuk AKIP.pdf (Path: AKIP PKTJ 2025\Indikator F\Surat Pernyataan Direktur\Pernyataan Direktur untuk AKIP.pdf)</t>
         </is>
       </c>
-      <c r="H84" s="52" t="inlineStr">
+      <c r="H84" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I84" s="52" t="n"/>
-      <c r="J84" s="52" t="n"/>
+      <c r="I84" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J84" s="70" t="inlineStr"/>
       <c r="K84" s="52" t="n"/>
       <c r="L84" s="52" t="n"/>
       <c r="M84" s="52" t="n"/>
@@ -5291,42 +5780,46 @@
       <c r="AB84" s="52" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="52" t="n"/>
-      <c r="B85" s="11" t="n">
+      <c r="A85" s="64" t="n"/>
+      <c r="B85" s="65" t="n">
         <v>37</v>
       </c>
-      <c r="C85" s="43" t="inlineStr">
+      <c r="C85" s="92" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Berita Acara Serah Terima Sementara atau Provisional Hand Over ?</t>
         </is>
       </c>
-      <c r="D85" s="16" t="inlineStr">
+      <c r="D85" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E85" s="16" t="inlineStr">
+      <c r="E85" s="64" t="inlineStr">
         <is>
           <t>Berita Acara Serah Terima Akhir (BAST / Final Hand Over)</t>
         </is>
       </c>
-      <c r="F85" s="16" t="inlineStr">
+      <c r="F85" s="64" t="inlineStr">
         <is>
           <t>Dokumen serah terima hasil pekerjaan 100% dari penyedia kepada PPK PKTJ.</t>
         </is>
       </c>
-      <c r="G85" s="37" t="inlineStr">
+      <c r="G85" s="85" t="inlineStr">
         <is>
           <t>F38.pdf (Path: AKIP PKTJ 2025\Indikator F\F38.pdf)</t>
         </is>
       </c>
-      <c r="H85" s="52" t="inlineStr">
+      <c r="H85" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/daftar-informasi/create</t>
         </is>
       </c>
-      <c r="I85" s="52" t="n"/>
-      <c r="J85" s="52" t="n"/>
+      <c r="I85" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J85" s="70" t="inlineStr"/>
       <c r="K85" s="52" t="n"/>
       <c r="L85" s="52" t="n"/>
       <c r="M85" s="52" t="n"/>
@@ -5347,38 +5840,42 @@
       <c r="AB85" s="52" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="52" t="n"/>
-      <c r="B86" s="11" t="n">
+      <c r="A86" s="60" t="n"/>
+      <c r="B86" s="61" t="n">
         <v>38</v>
       </c>
-      <c r="C86" s="43" t="inlineStr">
+      <c r="C86" s="95" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan dokumen Berita Acara Serah Terima atau Final Hand Over ?</t>
         </is>
       </c>
-      <c r="D86" s="16" t="inlineStr">
+      <c r="D86" s="63" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E86" s="21" t="inlineStr">
+      <c r="E86" s="63" t="inlineStr">
         <is>
           <t>SEKSI G: INFORMASI SETIAP SAAT (5 Poin)</t>
         </is>
       </c>
-      <c r="F86" s="16" t="inlineStr">
+      <c r="F86" s="63" t="inlineStr">
         <is>
           <t>PPK</t>
         </is>
       </c>
-      <c r="G86" s="16" t="n"/>
-      <c r="H86" s="52" t="inlineStr">
+      <c r="G86" s="63" t="n"/>
+      <c r="H86" s="60" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/setiap-saat</t>
         </is>
       </c>
-      <c r="I86" s="52" t="n"/>
-      <c r="J86" s="52" t="n"/>
+      <c r="I86" s="60" t="inlineStr">
+        <is>
+          <t>SEKSI G</t>
+        </is>
+      </c>
+      <c r="J86" s="60" t="n"/>
       <c r="K86" s="52" t="n"/>
       <c r="L86" s="52" t="n"/>
       <c r="M86" s="52" t="n"/>
@@ -5399,44 +5896,48 @@
       <c r="AB86" s="52" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="52" t="n"/>
-      <c r="B87" s="13" t="inlineStr">
+      <c r="A87" s="64" t="n"/>
+      <c r="B87" s="80" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="C87" s="48" t="inlineStr">
+      <c r="C87" s="96" t="inlineStr">
         <is>
           <t>INFORMASI SETIAP SAAT</t>
         </is>
       </c>
-      <c r="D87" s="35" t="inlineStr">
+      <c r="D87" s="82" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E87" s="16" t="inlineStr">
+      <c r="E87" s="64" t="inlineStr">
         <is>
           <t>Daftar Informasi Publik (DIP) &amp; Daftar Informasi Dikecualikan (DIK) PKTJ Tahun 2025/2026</t>
         </is>
       </c>
-      <c r="F87" s="16" t="inlineStr">
+      <c r="F87" s="64" t="inlineStr">
         <is>
           <t>Katalog klasifikasi seluruh dokumen informasi terbuka dan informasi yang dikecualikan di lingkungan PKTJ Tegal.</t>
         </is>
       </c>
-      <c r="G87" s="16" t="inlineStr">
+      <c r="G87" s="64" t="inlineStr">
         <is>
           <t>G1.pdf / G1(1).pdf / G1(2).pdf / G1.png (Path: AKIP PKTJ 2025\Indikator G\G1\G1.pdf)</t>
         </is>
       </c>
-      <c r="H87" s="52" t="inlineStr">
+      <c r="H87" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/setiap-saat/create</t>
         </is>
       </c>
-      <c r="I87" s="52" t="n"/>
-      <c r="J87" s="52" t="n"/>
+      <c r="I87" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J87" s="70" t="inlineStr"/>
       <c r="K87" s="52" t="n"/>
       <c r="L87" s="52" t="n"/>
       <c r="M87" s="52" t="n"/>
@@ -5457,42 +5958,46 @@
       <c r="AB87" s="52" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="52" t="n"/>
-      <c r="B88" s="11" t="n">
+      <c r="A88" s="64" t="n"/>
+      <c r="B88" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="C88" s="47" t="inlineStr">
+      <c r="C88" s="94" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara telah megusulkan Daftar Informasi Publik (DIP) dan Daftar Informasi Dikecualikan (DIK) 2025 kepada PPID Pelaksana ?</t>
         </is>
       </c>
-      <c r="D88" s="16" t="inlineStr">
+      <c r="D88" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E88" s="19" t="inlineStr">
+      <c r="E88" s="67" t="inlineStr">
         <is>
           <t>Buku Pedoman Standar Operasional Prosedur (SOP) Pelayanan Publik PKTJ Tegal</t>
         </is>
       </c>
-      <c r="F88" s="16" t="inlineStr">
+      <c r="F88" s="64" t="inlineStr">
         <is>
           <t>Kumpulan SOP layanan akademik, laboratorium keselamatan jalan, asrama, klinik kesehatan, perpustakaan, dan BLU.</t>
         </is>
       </c>
-      <c r="G88" s="37" t="inlineStr">
+      <c r="G88" s="85" t="inlineStr">
         <is>
           <t>G2.pdf (Path: AKIP PKTJ 2025\Indikator G\G2.pdf)</t>
         </is>
       </c>
-      <c r="H88" s="52" t="inlineStr">
+      <c r="H88" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/setiap-saat/create</t>
         </is>
       </c>
-      <c r="I88" s="52" t="n"/>
-      <c r="J88" s="52" t="n"/>
+      <c r="I88" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J88" s="70" t="inlineStr"/>
       <c r="K88" s="52" t="n"/>
       <c r="L88" s="52" t="n"/>
       <c r="M88" s="52" t="n"/>
@@ -5513,42 +6018,46 @@
       <c r="AB88" s="52" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="52" t="n"/>
-      <c r="B89" s="11" t="n">
+      <c r="A89" s="64" t="n"/>
+      <c r="B89" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="C89" s="47" t="inlineStr">
+      <c r="C89" s="94" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan peraturan/kebijakan/SOP yang telah disahkan dalam memberikan layanan publik kepada masyarakat ?</t>
         </is>
       </c>
-      <c r="D89" s="16" t="inlineStr">
+      <c r="D89" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E89" s="19" t="inlineStr">
+      <c r="E89" s="67" t="inlineStr">
         <is>
           <t>Buku Register Agenda Surat Masuk dan Surat Keluar Pimpinan PKTJ Tahun 2023-2025</t>
         </is>
       </c>
-      <c r="F89" s="16" t="inlineStr">
+      <c r="F89" s="64" t="inlineStr">
         <is>
           <t>Rekapitulasi arsip persuratan kedinasan resmi di lingkungan PKTJ Tegal.</t>
         </is>
       </c>
-      <c r="G89" s="37" t="inlineStr">
+      <c r="G89" s="85" t="inlineStr">
         <is>
           <t>Surat Masuk &amp; Keluar 2023-2025.pdf (Path: AKIP PKTJ 2025\Indikator G\G3\Surat Masuk tahun 2023-2025.pdf &amp; Surat Keluar.pdf)</t>
         </is>
       </c>
-      <c r="H89" s="52" t="inlineStr">
+      <c r="H89" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/setiap-saat/create</t>
         </is>
       </c>
-      <c r="I89" s="52" t="n"/>
-      <c r="J89" s="52" t="n"/>
+      <c r="I89" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J89" s="70" t="inlineStr"/>
       <c r="K89" s="52" t="n"/>
       <c r="L89" s="52" t="n"/>
       <c r="M89" s="52" t="n"/>
@@ -5569,42 +6078,46 @@
       <c r="AB89" s="52" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="52" t="n"/>
-      <c r="B90" s="11" t="n">
+      <c r="A90" s="64" t="n"/>
+      <c r="B90" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="C90" s="47" t="inlineStr">
+      <c r="C90" s="94" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan surat menyurat dari dan ke unit kerja tahun 2023 - 2025 ?</t>
         </is>
       </c>
-      <c r="D90" s="16" t="inlineStr">
+      <c r="D90" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E90" s="41" t="inlineStr">
+      <c r="E90" s="88" t="inlineStr">
         <is>
           <t>Laporan Barang Milik Negara (BMN) PKTJ Tegal Tahun 2024-2025 (Audited)</t>
         </is>
       </c>
-      <c r="F90" s="16" t="inlineStr">
+      <c r="F90" s="64" t="inlineStr">
         <is>
           <t>Laporan inventarisasi aset dan barang milik negara terdaftar di SIMAN Kemenkeu.</t>
         </is>
       </c>
-      <c r="G90" s="37" t="inlineStr">
+      <c r="G90" s="85" t="inlineStr">
         <is>
           <t>Laporan_BMN_PKTJ_2025_Audited.pdf (Path: AKIP PKTJ 2025\Indikator G\Laporan_BMN_PKTJ_2025.pdf)</t>
         </is>
       </c>
-      <c r="H90" s="52" t="inlineStr">
+      <c r="H90" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/setiap-saat/create</t>
         </is>
       </c>
-      <c r="I90" s="52" t="n"/>
-      <c r="J90" s="52" t="n"/>
+      <c r="I90" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J90" s="70" t="inlineStr"/>
       <c r="K90" s="52" t="n"/>
       <c r="L90" s="52" t="n"/>
       <c r="M90" s="52" t="n"/>
@@ -5625,42 +6138,46 @@
       <c r="AB90" s="52" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="52" t="n"/>
-      <c r="B91" s="11" t="n">
+      <c r="A91" s="60" t="n"/>
+      <c r="B91" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="C91" s="49" t="inlineStr">
+      <c r="C91" s="62" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara menyediakan Informasi Data Perbendaharaan atau Inventaris Barang Milik Negara Tahun 2024 ?</t>
         </is>
       </c>
-      <c r="D91" s="16" t="inlineStr">
+      <c r="D91" s="63" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E91" s="50" t="inlineStr">
+      <c r="E91" s="62" t="inlineStr">
         <is>
           <t>SEKSI H: INFORMASI SERTA MERTA (2 Poin)</t>
         </is>
       </c>
-      <c r="F91" s="16" t="inlineStr">
+      <c r="F91" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve"> BMN</t>
         </is>
       </c>
-      <c r="G91" s="37" t="inlineStr">
+      <c r="G91" s="63" t="inlineStr">
         <is>
           <t>https://pktj.ac.id/tentang/95-informasi-setiap-saat</t>
         </is>
       </c>
-      <c r="H91" s="52" t="inlineStr">
+      <c r="H91" s="60" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/serta-merta</t>
         </is>
       </c>
-      <c r="I91" s="52" t="n"/>
-      <c r="J91" s="52" t="n"/>
+      <c r="I91" s="60" t="inlineStr">
+        <is>
+          <t>SEKSI H</t>
+        </is>
+      </c>
+      <c r="J91" s="60" t="n"/>
       <c r="K91" s="52" t="n"/>
       <c r="L91" s="52" t="n"/>
       <c r="M91" s="52" t="n"/>
@@ -5681,44 +6198,48 @@
       <c r="AB91" s="52" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="52" t="n"/>
-      <c r="B92" s="13" t="inlineStr">
+      <c r="A92" s="64" t="n"/>
+      <c r="B92" s="80" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C92" s="14" t="inlineStr">
+      <c r="C92" s="81" t="inlineStr">
         <is>
           <t>Diumumkan Serta Merta</t>
         </is>
       </c>
-      <c r="D92" s="16" t="inlineStr">
+      <c r="D92" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E92" s="16" t="inlineStr">
+      <c r="E92" s="64" t="inlineStr">
         <is>
           <t>Pengumuman Kesiapsiagaan Kedaruratan &amp; Informasi Resmi Sipencatar PKTJ</t>
         </is>
       </c>
-      <c r="F92" s="16" t="inlineStr">
+      <c r="F92" s="64" t="inlineStr">
         <is>
           <t>Pengumuman kedaruratan keselamatan transportasi, cuaca ekstrem, dan informasi penting penerimaan calon taruna.</t>
         </is>
       </c>
-      <c r="G92" s="16" t="inlineStr">
+      <c r="G92" s="64" t="inlineStr">
         <is>
           <t>Postingan_Instagram_Sipencatar.png (Path: Medsos: https://www.instagram.com/p/DJqxqBLx-lC/ &amp; Web: /informasi-publik/serta-merta)</t>
         </is>
       </c>
-      <c r="H92" s="52" t="inlineStr">
+      <c r="H92" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/informasi/serta-merta/create</t>
         </is>
       </c>
-      <c r="I92" s="52" t="n"/>
-      <c r="J92" s="52" t="n"/>
+      <c r="I92" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J92" s="70" t="inlineStr"/>
       <c r="K92" s="52" t="n"/>
       <c r="L92" s="52" t="n"/>
       <c r="M92" s="52" t="n"/>
@@ -5739,42 +6260,46 @@
       <c r="AB92" s="52" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="52" t="n"/>
-      <c r="B93" s="11" t="n">
+      <c r="A93" s="60" t="n"/>
+      <c r="B93" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="C93" s="47" t="inlineStr">
+      <c r="C93" s="97" t="inlineStr">
         <is>
           <t>Apakah unit kerja Saudara mengumumkan informasi yang dapat mengancam hajat hidup orang banyak dan ketertiban umum di web/laman/direktori khusus/media sosial ?</t>
         </is>
       </c>
-      <c r="D93" s="16" t="inlineStr">
+      <c r="D93" s="63" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E93" s="19" t="inlineStr">
+      <c r="E93" s="62" t="inlineStr">
         <is>
           <t>SEKSI I: INOVASI DALAM PELAYANAN (3 Poin)</t>
         </is>
       </c>
-      <c r="F93" s="16" t="inlineStr">
+      <c r="F93" s="63" t="inlineStr">
         <is>
           <t>konten berupa informasi perubahan jadwal kegiatan</t>
         </is>
       </c>
-      <c r="G93" s="21" t="inlineStr">
+      <c r="G93" s="63" t="inlineStr">
         <is>
           <t>https://pktj.ac.id/tentang/96-informasi-serta-merta</t>
         </is>
       </c>
-      <c r="H93" s="52" t="inlineStr">
+      <c r="H93" s="60" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/aksesibilitas</t>
         </is>
       </c>
-      <c r="I93" s="52" t="n"/>
-      <c r="J93" s="52" t="inlineStr">
+      <c r="I93" s="60" t="inlineStr">
+        <is>
+          <t>SEKSI I</t>
+        </is>
+      </c>
+      <c r="J93" s="60" t="inlineStr">
         <is>
           <t>INFORMASI SERTA MERTA YANG USULAN DIP DIHAPUS.
 GANTI JADI LINK INSTAGRAM DI SAMPING, TULISANNYA 'INFORMASI SIPENCATAR'</t>
@@ -5800,44 +6325,48 @@
       <c r="AB93" s="52" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="52" t="n"/>
-      <c r="B94" s="13" t="inlineStr">
+      <c r="A94" s="64" t="n"/>
+      <c r="B94" s="80" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="C94" s="14" t="inlineStr">
+      <c r="C94" s="81" t="inlineStr">
         <is>
           <t>Inovasi Dalam Pelayanan</t>
         </is>
       </c>
-      <c r="D94" s="16" t="inlineStr">
+      <c r="D94" s="64" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="E94" s="16" t="inlineStr">
+      <c r="E94" s="64" t="inlineStr">
         <is>
           <t>Dokumen Formulir Permohonan &amp; Keberatan Huruf Braille (Standar &amp; Full) serta Laporan Inovasi Layanan Ramah Disabilitas PPID PKTJ Tegal</t>
         </is>
       </c>
-      <c r="F94" s="16" t="inlineStr">
+      <c r="F94" s="64" t="inlineStr">
         <is>
           <t>Inovasi pemenuhan sarana aksesibilitas terpadu bagi penyandang disabilitas: Formulir Permohonan Braille (Standar &amp; Full Format), Pernyataan Keberatan Braille (Standar &amp; Full Format), Audio Text-to-Speech otomatis, serta Video Panduan Bahasa Isyarat (Bisindo). Diunggah/diinput linknya melalui Menu Admin Layanan Inklusif (Braille).</t>
         </is>
       </c>
-      <c r="G94" s="16" t="inlineStr">
+      <c r="G94" s="64" t="inlineStr">
         <is>
           <t>FORMULIR PERMOHONAN INFORMASI PUBLIK BRAILE.pdf, FORMULIR PERMOHONAN INFORMASI PUBLIK FULL BRAILE.pdf, PERNYATAAN KEBERATAN ATAS PERMOHONAN INFORMASI BRAILE.pdf, PERNYATAAN KEBERATAN ATAS PERMOHONAN INFORMASI FULL BRAILE.pdf, &amp; Inovasi PPID.docx (Path: AKIP PKTJ 2025\Indikator I)</t>
         </is>
       </c>
-      <c r="H94" s="52" t="inlineStr">
+      <c r="H94" s="64" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/aksesibilitas</t>
         </is>
       </c>
-      <c r="I94" s="52" t="n"/>
-      <c r="J94" s="52" t="n"/>
+      <c r="I94" s="69" t="inlineStr">
+        <is>
+          <t>☐ BELUM DIUPLOAD</t>
+        </is>
+      </c>
+      <c r="J94" s="70" t="inlineStr"/>
       <c r="K94" s="52" t="n"/>
       <c r="L94" s="52" t="n"/>
       <c r="M94" s="52" t="n"/>
@@ -34390,9 +34919,12 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F3"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="D6:D14 D16:D20 D22:D30 D32:D36 D38:D86 D88:D91 D93 D95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Ya,Tidak"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I5:I105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Pilihan Status Tidak Valid" error="Silakan pilih status dari dropdown yang tersedia" promptTitle="Status Upload Realtime" prompt="Pilih status upload dokumen ini" type="list">
+      <formula1>"☑ SUDAH DIUPLOAD,☐ BELUM DIUPLOAD,⏳ SEDANG PROSES"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>

--- a/FILE_1_SPREADSHEET_AKIP_2025_LOKASI_FILE_LAPTOP.xlsx
+++ b/FILE_1_SPREADSHEET_AKIP_2025_LOKASI_FILE_LAPTOP.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -104,6 +104,12 @@
       <color rgb="00004A99"/>
       <sz val="8.5"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -163,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -200,6 +206,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -622,6 +629,7 @@
         <v/>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -734,7 +742,7 @@
 (Path: AKIP PKTJ 2025\Indikator A\A1.pdf)</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/regulasi</t>
         </is>
@@ -783,7 +791,7 @@
 (Path: AKIP PKTJ 2025\Indikator A\A2.pdf (juga di: extracted_all\Bahan Website PPID PKTJ\PM_46_TAHUN_2018.pdf))</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/regulasi</t>
         </is>
@@ -832,7 +840,7 @@
 (Path: AKIP PKTJ 2025\Indikator A\A3.pdf)</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/regulasi</t>
         </is>
@@ -881,7 +889,7 @@
 (Path: Tayang di Halaman Publik: /profil-ppid.html)</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/profil/edit/profil_singkat</t>
         </is>
@@ -930,7 +938,7 @@
 (Path: Tayang di Halaman Publik: /profil-tugas-tanggung-jawab.html)</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/profil/edit/tugas_fungsi</t>
         </is>
@@ -979,7 +987,7 @@
 (Path: AKIP PKTJ 2025\Indikator A\A6.jpeg)</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/profil/edit/struktur_organisasi</t>
         </is>
@@ -1028,7 +1036,7 @@
 (Path: Tayang di Halaman Publik: /profil-visi-misi.html)</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/profil/edit/visi_misi</t>
         </is>
@@ -1077,9 +1085,9 @@
 (Path: AKIP PKTJ 2025\Indikator A\A8.JPG (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\Agenda Kegiatan PPID dan Humas 2026.xlsx))</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/berkala/12/edit</t>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/A8/edit</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -1126,9 +1134,9 @@
 (Path: AKIP PKTJ 2025\Indikator A\A9\A9 2024.jpg &amp; A9 2025.jpg)</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/berkala/12/edit</t>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/A9/edit</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -1203,9 +1211,9 @@
 (Path: AKIP PKTJ 2025\Indikator B\B1-B4.pdf (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2026\Dokumen Daftar Informasi Berkala TERSENSOR\DIPA.pdf))</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/berkala/12/edit</t>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/B1/edit</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -1252,7 +1260,7 @@
 (Path: AKIP PKTJ 2025\Indikator B\B1-B4.pdf (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2026\Penyampaian Laporan Permohonan Informasi PKTJ Tahun 2025.pdf))</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/laporan-layanan</t>
         </is>
@@ -1301,7 +1309,7 @@
 (Path: AKIP PKTJ 2025\Indikator B\B1-B4.pdf)</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/prosedur/sop-sengketa</t>
         </is>
@@ -1350,9 +1358,9 @@
 (Path: AKIP PKTJ 2025\Indikator B\B1-B4.pdf (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2026\20251210221658Usulan DIP dan DIK 2026 PKTJ.pdf))</t>
         </is>
       </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/setiap-saat/3/edit</t>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/B4/edit</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -1399,9 +1407,9 @@
 (Path: AKIP PKTJ 2025\Indikator B\B5\B5.pdf)</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/berkala/6/edit</t>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/B5/edit</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -1476,7 +1484,7 @@
 (Path: AKIP PKTJ 2025\Indikator C\C1.png &amp; C2.JPG)</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/maklumat-pelayanan</t>
         </is>
@@ -1525,7 +1533,7 @@
 (Path: AKIP PKTJ 2025\Indikator C\C3.pdf)</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/prosedur/sop-permintaan</t>
         </is>
@@ -1574,7 +1582,7 @@
 (Path: AKIP PKTJ 2025\Indikator C\Register_Permohonan_NIHIL.pdf)</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/laporan-layanan</t>
         </is>
@@ -1623,7 +1631,7 @@
 (Path: Tayang di Website &amp; Pigura Fisik Ruang Layanan PPID)</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/maklumat-pelayanan</t>
         </is>
@@ -1672,7 +1680,7 @@
 (Path: Tayang di Website &amp; Papan Pengumuman Meja Layanan PPID)</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/maklumat-pelayanan</t>
         </is>
@@ -1721,7 +1729,7 @@
 (Path: AKIP PKTJ 2025\Indikator C\C6.pdf (juga tayang di: /sop-permintaan.html))</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/prosedur/sop-permintaan</t>
         </is>
@@ -1770,7 +1778,7 @@
 (Path: AKIP PKTJ 2025\Indikator C\C7.pdf (juga tayang di: /sop-keberatan.html))</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/prosedur/sop-keberatan</t>
         </is>
@@ -1819,7 +1827,7 @@
 (Path: AKIP PKTJ 2025\Indikator C\C8.pdf (juga tayang di: /sop-sengketa.html))</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/prosedur/sop-sengketa</t>
         </is>
@@ -1868,7 +1876,7 @@
 (Path: AKIP PKTJ 2025\Indikator C\C9.pdf (juga tayang di: /sop-penetapan.html))</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/prosedur/sop-penetapan</t>
         </is>
@@ -1917,7 +1925,7 @@
 (Path: AKIP PKTJ 2025\Indikator C\C10.pdf (juga tayang di: /sop-pengujian.html))</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/prosedur/sop-pengujian</t>
         </is>
@@ -1966,7 +1974,7 @@
 (Path: AKIP PKTJ 2025\Indikator C\C11.pdf (juga tayang di: /sop-pendokumentasian.html))</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/prosedur/sop-pendokumentasian</t>
         </is>
@@ -2043,7 +2051,7 @@
 (Path: AKIP PKTJ 2025\Indikator D\D1.pdf)</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/aksesibilitas</t>
         </is>
@@ -2092,7 +2100,7 @@
 (Path: AKIP PKTJ 2025\Indikator I\FORMULIR PERMOHONAN INFORMASI PUBLIK BRAILE.pdf (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2025\Formulir Permohonan Informasi Braile PKTJ.docx))</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/aksesibilitas</t>
         </is>
@@ -2141,7 +2149,7 @@
 (Path: AKIP PKTJ 2025\Indikator I\PERNYATAAN KEBERATAN ATAS PERMOHONAN INFORMASI BRAILE.pdf (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2025\Formulir Keberatan Braile PKTJ.docx))</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr">
+      <c r="G36" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/aksesibilitas</t>
         </is>
@@ -2190,7 +2198,7 @@
 (Path: AKIP PKTJ 2025\Indikator D\D4.pdf)</t>
         </is>
       </c>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="G37" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/aksesibilitas</t>
         </is>
@@ -2239,7 +2247,7 @@
 (Path: AKIP PKTJ 2025\Indikator D\D5.jpg)</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="G38" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/aksesibilitas</t>
         </is>
@@ -2316,7 +2324,7 @@
 (Path: AKIP PKTJ 2025\Indikator E\E.1.3.png)</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G40" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/dashboard</t>
         </is>
@@ -2365,7 +2373,7 @@
 (Path: AKIP PKTJ 2025\Indikator E\E2.pdf)</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr">
+      <c r="G41" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/dashboard</t>
         </is>
@@ -2414,7 +2422,7 @@
 (Path: AKIP PKTJ 2025\Indikator E\E3.pdf (tayang di: /permohonan-informasi))</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="G42" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/permohonan-informasi</t>
         </is>
@@ -2463,7 +2471,7 @@
 (Path: AKIP PKTJ 2025\Indikator E\E4.pdf (tayang di: /permohonan/keberatan))</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="G43" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/keberatan</t>
         </is>
@@ -2512,7 +2520,7 @@
 (Path: AKIP PKTJ 2025\Indikator E\E5\E5.JPG)</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G44" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/kontak</t>
         </is>
@@ -2561,7 +2569,7 @@
 (Path: AKIP PKTJ 2025\Indikator E\E6.pdf)</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
+      <c r="G45" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/kontak</t>
         </is>
@@ -2610,7 +2618,7 @@
 (Path: AKIP PKTJ 2025\Indikator E\E7.pdf (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2026\LAPORAN pertanyaan masuk di sosmed PKTJ TAHUN 2026.xlsx))</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="G46" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/laporan-layanan</t>
         </is>
@@ -2687,9 +2695,9 @@
 (Path: AKIP PKTJ 2025\Indikator F\F1.pdf)</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/berkala/5/edit</t>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/F1/edit</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
@@ -2736,9 +2744,9 @@
 (Path: AKIP PKTJ 2025\Indikator F\F2.pdf (juga di: extracted_key_docs\CV_*.xlsx))</t>
         </is>
       </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/berkala/6/edit</t>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/F2/edit</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
@@ -2785,7 +2793,7 @@
 (Path: AKIP PKTJ 2025\Indikator F\F3.xlsx (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2026\Dokumen Daftar Informasi Berkala TERSENSOR\LHKPN.pdf))</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="G50" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/pejabat</t>
         </is>
@@ -2834,9 +2842,9 @@
 (Path: AKIP PKTJ 2025\Indikator F\F4.pdf (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2026\Dokumen Daftar Informasi Berkala TERSENSOR\Renstra.pdf))</t>
         </is>
       </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/berkala/7/edit</t>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/F4/edit</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
@@ -2883,9 +2891,9 @@
 (Path: AKIP PKTJ 2025\Indikator F\F4.pdf (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2026\Dokumen Daftar Informasi Berkala TERSENSOR\RKT.pdf))</t>
         </is>
       </c>
-      <c r="G52" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/berkala/8/edit</t>
+      <c r="G52" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/F5/edit</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
@@ -2932,9 +2940,9 @@
 (Path: AKIP PKTJ 2025\Indikator F\F6.pdf (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2026\Dokumen Daftar Informasi Berkala TERSENSOR\LAKIP.pdf))</t>
         </is>
       </c>
-      <c r="G53" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/berkala/9/edit</t>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/F6/edit</t>
         </is>
       </c>
       <c r="H53" s="12" t="inlineStr">
@@ -2981,9 +2989,9 @@
 (Path: AKIP PKTJ 2025\Indikator F\F7.pdf (juga di: extracted_all\Bahan Website PPID PKTJ\1. LAI LALPORAN KEUANGAN PKTJ 2024.pdf))</t>
         </is>
       </c>
-      <c r="G54" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/berkala/10/edit</t>
+      <c r="G54" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/F7/edit</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
@@ -3030,9 +3038,9 @@
 (Path: AKIP PKTJ 2025\Indikator F\F8.xlsx (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2026\Dokumen Daftar Informasi Berkala TERSENSOR\DIPA.pdf))</t>
         </is>
       </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/berkala/11/edit</t>
+      <c r="G55" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/F8/edit</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
@@ -3079,9 +3087,9 @@
 (Path: AKIP PKTJ 2025\Indikator F\F9.xlsx (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2026\Dokumen Daftar Informasi Berkala TERSENSOR\RUP.pdf))</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/berkala/13/edit</t>
+      <c r="G56" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/F9/edit</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
@@ -3128,9 +3136,9 @@
 (Path: AKIP PKTJ 2025\Indikator F\F10.pdf)</t>
         </is>
       </c>
-      <c r="G57" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/berkala/14/edit</t>
+      <c r="G57" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/F10/edit</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
@@ -3205,9 +3213,9 @@
 (Path: AKIP PKTJ 2025\Indikator G\G1\G1.pdf (juga di: extracted_all\Bahan Website PPID PKTJ\DIP Kemenhub Tahun 2026.pdf &amp; DIK Kemenhub Tahun 2026.pdf))</t>
         </is>
       </c>
-      <c r="G59" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/setiap-saat/3/edit</t>
+      <c r="G59" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/G1/edit</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
@@ -3254,9 +3262,9 @@
 (Path: AKIP PKTJ 2025\Indikator G\G2.pdf (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2026\Dokumen Daftar Informasi Setiap Saat TERSENSOR\BMN.pdf))</t>
         </is>
       </c>
-      <c r="G60" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/setiap-saat/6/edit</t>
+      <c r="G60" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/G2/edit</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
@@ -3303,9 +3311,9 @@
 (Path: AKIP PKTJ 2025\Indikator G\G3\Surat Masuk tahun 2025.pdf &amp; Surat Keluar tahun 2025.pdf)</t>
         </is>
       </c>
-      <c r="G61" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/setiap-saat/5/edit</t>
+      <c r="G61" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/G3/edit</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr">
@@ -3380,9 +3388,9 @@
 (Path: AKIP PKTJ 2025\Indikator H\H1.pdf (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2024\DIP Serta Merta 2024 PKTJ Tegal.pdf))</t>
         </is>
       </c>
-      <c r="G63" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/serta-merta/3/edit</t>
+      <c r="G63" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/H1/edit</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
@@ -3429,9 +3437,9 @@
 (Path: AKIP PKTJ 2025\Indikator H\H2.pdf (juga di: extracted_key_docs\Laporan Kegiatan P4GN 2025.docx.pdf))</t>
         </is>
       </c>
-      <c r="G64" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/serta-merta/4/edit</t>
+      <c r="G64" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/H2/edit</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
@@ -3478,9 +3486,9 @@
 (Path: AKIP PKTJ 2025\Indikator H\H3.pdf)</t>
         </is>
       </c>
-      <c r="G65" s="12" t="inlineStr">
-        <is>
-          <t>http://ppid.pktj.ac.id/admin/informasi/serta-merta/5/edit</t>
+      <c r="G65" s="20" t="inlineStr">
+        <is>
+          <t>http://ppid.pktj.ac.id/admin/akip/H3/edit</t>
         </is>
       </c>
       <c r="H65" s="12" t="inlineStr">
@@ -3555,7 +3563,7 @@
 (Path: AKIP PKTJ 2025\Indikator I (juga di: extracted_all\Bahan Website PPID PKTJ\PPID\2025\Formulir Permohonan Informasi Braile PKTJ.docx &amp; Formulir Keberatan Braile PKTJ.docx))</t>
         </is>
       </c>
-      <c r="G67" s="12" t="inlineStr">
+      <c r="G67" s="20" t="inlineStr">
         <is>
           <t>http://ppid.pktj.ac.id/admin/layanan/aksesibilitas</t>
         </is>
@@ -3578,6 +3586,62 @@
       <formula1>"☑ SUDAH DIUPLOAD,☐ BELUM DIUPLOAD,⏳ SEDANG PROSES"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3614,6 +3678,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -29097,6 +29162,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
